--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -30,6 +30,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
+    <author>Administrator</author>
   </authors>
   <commentList>
     <comment ref="C3" authorId="0">
@@ -100,12 +101,80 @@
         </r>
       </text>
     </comment>
+    <comment ref="AD4" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+特效ID</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AE4" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+特效值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AF4" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+特效最大叠加层数
+0 无限次
+1 单次</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="89">
   <si>
     <t>_ID</t>
   </si>
@@ -149,15 +218,21 @@
     <t>增加伤害比例</t>
   </si>
   <si>
+    <t>无视防御</t>
+  </si>
+  <si>
+    <t>暴击率</t>
+  </si>
+  <si>
+    <t>暴击倍率</t>
+  </si>
+  <si>
     <t>致命率</t>
   </si>
   <si>
     <t>致命伤害</t>
   </si>
   <si>
-    <t>无视防御</t>
-  </si>
-  <si>
     <t>伤害加成</t>
   </si>
   <si>
@@ -167,6 +242,18 @@
     <t>最终加成</t>
   </si>
   <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>Speed</t>
+  </si>
+  <si>
+    <t>附加属性</t>
+  </si>
+  <si>
+    <t>属性值</t>
+  </si>
+  <si>
     <t>附带效果</t>
   </si>
   <si>
@@ -209,16 +296,22 @@
     <t>Percent</t>
   </si>
   <si>
+    <t>IgnoreDef</t>
+  </si>
+  <si>
+    <t>CritRate</t>
+  </si>
+  <si>
+    <t>CritDamage</t>
+  </si>
+  <si>
     <t>DeadlyRate</t>
   </si>
   <si>
     <t>DeadlyDamage</t>
   </si>
   <si>
-    <t>IgnoreDef</t>
-  </si>
-  <si>
-    <t>DamageIncrea</t>
+    <t>RateDamage</t>
   </si>
   <si>
     <t>AttrIncrea</t>
@@ -227,13 +320,28 @@
     <t>FinalIncrea</t>
   </si>
   <si>
+    <t>AttrId</t>
+  </si>
+  <si>
+    <t>AttrValue</t>
+  </si>
+  <si>
     <t>EffectId</t>
   </si>
   <si>
+    <t>EffectValue</t>
+  </si>
+  <si>
+    <t>EffectMax</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
+  </si>
+  <si>
+    <t>double</t>
   </si>
   <si>
     <t>基础心法</t>
@@ -511,12 +619,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1309,7 +1417,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:X61"/>
+  <dimension ref="C3:AF61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
@@ -1324,17 +1432,21 @@
     <col min="15" max="15" width="8" style="1" customWidth="1"/>
     <col min="16" max="16" width="7.75" style="1" customWidth="1"/>
     <col min="17" max="17" width="10.375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="11.25" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="7.75" style="1" customWidth="1"/>
-    <col min="21" max="21" width="12.625" style="1" customWidth="1"/>
-    <col min="22" max="22" width="9.25" style="1" customWidth="1"/>
-    <col min="23" max="23" width="10.75" style="1" customWidth="1"/>
-    <col min="24" max="24" width="7.375" style="1" customWidth="1"/>
-    <col min="25" max="16384" width="9" style="1"/>
+    <col min="18" max="18" width="7.75" style="1" customWidth="1"/>
+    <col min="19" max="19" width="7.50833333333333" style="1" customWidth="1"/>
+    <col min="20" max="20" width="10.625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="11.25" style="1" customWidth="1"/>
+    <col min="22" max="22" width="10.625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="12.625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="9.25" style="1" customWidth="1"/>
+    <col min="25" max="25" width="10.75" style="1" customWidth="1"/>
+    <col min="26" max="29" width="10.0833333333333" style="1" customWidth="1"/>
+    <col min="30" max="31" width="9" style="1" customWidth="1"/>
+    <col min="32" max="32" width="7.58333333333333" style="1" customWidth="1"/>
+    <col min="33" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:24">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1399,140 +1511,208 @@
       <c r="X3" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="Y3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C4" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="V4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="W4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="X4" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="AB4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF4" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C5" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:24">
+        <v>53</v>
+      </c>
+      <c r="Y5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AE5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF5" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:32">
       <c r="C6" s="1">
         <v>10011</v>
       </c>
@@ -1543,13 +1723,13 @@
         <v>1001</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I6" s="1">
         <v>4</v>
@@ -1599,8 +1779,11 @@
       <c r="X6" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:24">
+      <c r="Y6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:32">
       <c r="C7" s="1">
         <v>10021</v>
       </c>
@@ -1611,13 +1794,13 @@
         <v>1002</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="I7" s="1">
         <v>4</v>
@@ -1667,8 +1850,11 @@
       <c r="X7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:24">
+      <c r="Y7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:32">
       <c r="C8" s="1">
         <v>10031</v>
       </c>
@@ -1679,13 +1865,13 @@
         <v>1003</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="I8" s="1">
         <v>4</v>
@@ -1735,8 +1921,11 @@
       <c r="X8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:24">
+      <c r="Y8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:32">
       <c r="C9" s="1">
         <v>10041</v>
       </c>
@@ -1747,13 +1936,13 @@
         <v>1004</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="I9" s="1">
         <v>4</v>
@@ -1803,8 +1992,11 @@
       <c r="X9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:24">
+      <c r="Y9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:32">
       <c r="C10" s="1">
         <v>10071</v>
       </c>
@@ -1815,13 +2007,13 @@
         <v>1007</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="I10" s="1">
         <v>4</v>
@@ -1871,12 +2063,24 @@
       <c r="X10" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:24">
+      <c r="Y10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:32">
       <c r="F11" s="4"/>
-      <c r="V11" s="4"/>
-    </row>
-    <row r="12" customHeight="1" spans="3:24">
+      <c r="R11" s="1">
+        <v>0</v>
+      </c>
+      <c r="S11" s="1">
+        <v>0</v>
+      </c>
+      <c r="T11" s="1">
+        <v>0</v>
+      </c>
+      <c r="X11" s="4"/>
+    </row>
+    <row r="12" customHeight="1" spans="3:32">
       <c r="C12" s="1">
         <v>10022</v>
       </c>
@@ -1887,13 +2091,13 @@
         <v>1002</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I12" s="1">
         <v>4</v>
@@ -1943,8 +2147,11 @@
       <c r="X12" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:24">
+      <c r="Y12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:32">
       <c r="C13" s="1">
         <v>10032</v>
       </c>
@@ -1955,13 +2162,13 @@
         <v>1003</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I13" s="1">
         <v>4</v>
@@ -1990,15 +2197,9 @@
       <c r="Q13" s="4">
         <v>10</v>
       </c>
-      <c r="R13" s="1">
-        <v>0</v>
-      </c>
-      <c r="S13" s="1">
-        <v>0</v>
-      </c>
-      <c r="T13" s="1">
-        <v>0</v>
-      </c>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
       <c r="U13" s="1">
         <v>0</v>
       </c>
@@ -2011,8 +2212,11 @@
       <c r="X13" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:24">
+      <c r="Y13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:32">
       <c r="C14" s="1">
         <v>10042</v>
       </c>
@@ -2023,13 +2227,13 @@
         <v>1004</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I14" s="1">
         <v>4</v>
@@ -2079,8 +2283,11 @@
       <c r="X14" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:24">
+      <c r="Y14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:32">
       <c r="C15" s="1">
         <v>10052</v>
       </c>
@@ -2091,13 +2298,13 @@
         <v>1005</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I15" s="1">
         <v>4</v>
@@ -2147,8 +2354,11 @@
       <c r="X15" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:24">
+      <c r="Y15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:32">
       <c r="C16" s="1">
         <v>10062</v>
       </c>
@@ -2159,13 +2369,13 @@
         <v>1006</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I16" s="1">
         <v>4</v>
@@ -2215,8 +2425,11 @@
       <c r="X16" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:24">
+      <c r="Y16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:32">
       <c r="C17" s="1">
         <v>10072</v>
       </c>
@@ -2227,13 +2440,13 @@
         <v>1007</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I17" s="1">
         <v>4</v>
@@ -2283,12 +2496,15 @@
       <c r="X17" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:24">
+      <c r="Y17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:32">
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
     </row>
-    <row r="19" customHeight="1" spans="3:24">
+    <row r="19" customHeight="1" spans="3:32">
       <c r="C19" s="1">
         <v>10023</v>
       </c>
@@ -2299,13 +2515,13 @@
         <v>1002</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I19" s="1">
         <v>4</v>
@@ -2335,17 +2551,17 @@
         <v>0</v>
       </c>
       <c r="R19" s="1">
+        <v>0</v>
+      </c>
+      <c r="S19" s="1">
+        <v>0</v>
+      </c>
+      <c r="T19" s="1">
+        <v>0</v>
+      </c>
+      <c r="U19" s="1">
         <v>10</v>
       </c>
-      <c r="S19" s="1">
-        <v>0</v>
-      </c>
-      <c r="T19" s="1">
-        <v>0</v>
-      </c>
-      <c r="U19" s="1">
-        <v>0</v>
-      </c>
       <c r="V19" s="1">
         <v>0</v>
       </c>
@@ -2355,8 +2571,11 @@
       <c r="X19" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:24">
+      <c r="Y19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:32">
       <c r="C20" s="1">
         <v>10033</v>
       </c>
@@ -2367,13 +2586,13 @@
         <v>1003</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I20" s="1">
         <v>4</v>
@@ -2403,17 +2622,17 @@
         <v>0</v>
       </c>
       <c r="R20" s="1">
+        <v>0</v>
+      </c>
+      <c r="S20" s="1">
+        <v>0</v>
+      </c>
+      <c r="T20" s="1">
+        <v>0</v>
+      </c>
+      <c r="U20" s="1">
         <v>10</v>
       </c>
-      <c r="S20" s="1">
-        <v>0</v>
-      </c>
-      <c r="T20" s="1">
-        <v>0</v>
-      </c>
-      <c r="U20" s="1">
-        <v>0</v>
-      </c>
       <c r="V20" s="1">
         <v>0</v>
       </c>
@@ -2423,8 +2642,11 @@
       <c r="X20" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:24">
+      <c r="Y20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:32">
       <c r="C21" s="1">
         <v>10043</v>
       </c>
@@ -2435,13 +2657,13 @@
         <v>1004</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I21" s="1">
         <v>4</v>
@@ -2471,17 +2693,17 @@
         <v>0</v>
       </c>
       <c r="R21" s="1">
+        <v>0</v>
+      </c>
+      <c r="S21" s="1">
+        <v>0</v>
+      </c>
+      <c r="T21" s="1">
+        <v>0</v>
+      </c>
+      <c r="U21" s="1">
         <v>10</v>
       </c>
-      <c r="S21" s="1">
-        <v>0</v>
-      </c>
-      <c r="T21" s="1">
-        <v>0</v>
-      </c>
-      <c r="U21" s="1">
-        <v>0</v>
-      </c>
       <c r="V21" s="1">
         <v>0</v>
       </c>
@@ -2491,8 +2713,11 @@
       <c r="X21" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:24">
+      <c r="Y21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:32">
       <c r="C22" s="1">
         <v>10073</v>
       </c>
@@ -2503,13 +2728,13 @@
         <v>1007</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I22" s="1">
         <v>4</v>
@@ -2539,17 +2764,17 @@
         <v>0</v>
       </c>
       <c r="R22" s="1">
+        <v>0</v>
+      </c>
+      <c r="S22" s="1">
+        <v>0</v>
+      </c>
+      <c r="T22" s="1">
+        <v>0</v>
+      </c>
+      <c r="U22" s="1">
         <v>10</v>
       </c>
-      <c r="S22" s="1">
-        <v>0</v>
-      </c>
-      <c r="T22" s="1">
-        <v>0</v>
-      </c>
-      <c r="U22" s="1">
-        <v>0</v>
-      </c>
       <c r="V22" s="1">
         <v>0</v>
       </c>
@@ -2559,12 +2784,23 @@
       <c r="X22" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:24">
-      <c r="V23" s="4"/>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1"/>
-    <row r="26" customHeight="1" spans="3:24">
+      <c r="Y22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:32">
+      <c r="X23" s="4"/>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:32">
+      <c r="Z24" s="1"/>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="1"/>
+      <c r="AC24" s="1"/>
+      <c r="AD24" s="1"/>
+      <c r="AE24" s="1"/>
+      <c r="AF24" s="1"/>
+    </row>
+    <row r="26" customHeight="1" spans="3:32">
       <c r="C26" s="1">
         <v>20011</v>
       </c>
@@ -2575,13 +2811,13 @@
         <v>2001</v>
       </c>
       <c r="F26" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="H26" s="1" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="I26" s="1">
         <v>4</v>
@@ -2631,8 +2867,11 @@
       <c r="X26" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:24">
+      <c r="Y26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:32">
       <c r="C27" s="1">
         <v>20021</v>
       </c>
@@ -2643,13 +2882,13 @@
         <v>2002</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="I27" s="1">
         <v>4</v>
@@ -2699,8 +2938,11 @@
       <c r="X27" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:24">
+      <c r="Y27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:32">
       <c r="C28" s="1">
         <v>20031</v>
       </c>
@@ -2711,13 +2953,13 @@
         <v>2003</v>
       </c>
       <c r="F28" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H28" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="I28" s="1">
         <v>4</v>
@@ -2767,8 +3009,11 @@
       <c r="X28" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:24">
+      <c r="Y28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:32">
       <c r="C29" s="1">
         <v>20041</v>
       </c>
@@ -2779,13 +3024,13 @@
         <v>2004</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="I29" s="1">
         <v>4</v>
@@ -2835,8 +3080,11 @@
       <c r="X29" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:24">
+      <c r="Y29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:32">
       <c r="C30" s="1">
         <v>20071</v>
       </c>
@@ -2847,13 +3095,13 @@
         <v>2007</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="I30" s="1">
         <v>4</v>
@@ -2903,12 +3151,24 @@
       <c r="X30" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:24">
+      <c r="Y30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:32">
       <c r="F31" s="4"/>
-      <c r="V31" s="4"/>
-    </row>
-    <row r="32" customHeight="1" spans="3:24">
+      <c r="R31" s="1">
+        <v>0</v>
+      </c>
+      <c r="S31" s="1">
+        <v>0</v>
+      </c>
+      <c r="T31" s="1">
+        <v>0</v>
+      </c>
+      <c r="X31" s="4"/>
+    </row>
+    <row r="32" customHeight="1" spans="3:32">
       <c r="C32" s="1">
         <v>20022</v>
       </c>
@@ -2919,13 +3179,13 @@
         <v>2002</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I32" s="1">
         <v>4</v>
@@ -2975,8 +3235,11 @@
       <c r="X32" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:24">
+      <c r="Y32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:32">
       <c r="C33" s="1">
         <v>20032</v>
       </c>
@@ -2987,13 +3250,13 @@
         <v>2003</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I33" s="1">
         <v>4</v>
@@ -3043,8 +3306,11 @@
       <c r="X33" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:24">
+      <c r="Y33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:32">
       <c r="C34" s="1">
         <v>20042</v>
       </c>
@@ -3055,13 +3321,13 @@
         <v>2004</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I34" s="1">
         <v>4</v>
@@ -3111,8 +3377,11 @@
       <c r="X34" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:24">
+      <c r="Y34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:32">
       <c r="C35" s="1">
         <v>20052</v>
       </c>
@@ -3123,13 +3392,13 @@
         <v>2005</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I35" s="1">
         <v>4</v>
@@ -3179,8 +3448,11 @@
       <c r="X35" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:24">
+      <c r="Y35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:32">
       <c r="C36" s="1">
         <v>20062</v>
       </c>
@@ -3191,13 +3463,13 @@
         <v>2006</v>
       </c>
       <c r="F36" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="H36" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I36" s="1">
         <v>4</v>
@@ -3247,8 +3519,11 @@
       <c r="X36" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:24">
+      <c r="Y36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:32">
       <c r="C37" s="1">
         <v>20072</v>
       </c>
@@ -3259,13 +3534,13 @@
         <v>2007</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I37" s="1">
         <v>4</v>
@@ -3315,12 +3590,24 @@
       <c r="X37" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:24">
+      <c r="Y37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:32">
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
-    </row>
-    <row r="39" customHeight="1" spans="3:24">
+      <c r="R38" s="1">
+        <v>0</v>
+      </c>
+      <c r="S38" s="1">
+        <v>0</v>
+      </c>
+      <c r="T38" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:32">
       <c r="C39" s="1">
         <v>20023</v>
       </c>
@@ -3331,13 +3618,13 @@
         <v>2002</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I39" s="1">
         <v>4</v>
@@ -3367,17 +3654,17 @@
         <v>0</v>
       </c>
       <c r="R39" s="1">
+        <v>0</v>
+      </c>
+      <c r="S39" s="1">
+        <v>0</v>
+      </c>
+      <c r="T39" s="1">
+        <v>0</v>
+      </c>
+      <c r="U39" s="1">
         <v>10</v>
       </c>
-      <c r="S39" s="1">
-        <v>0</v>
-      </c>
-      <c r="T39" s="1">
-        <v>0</v>
-      </c>
-      <c r="U39" s="1">
-        <v>0</v>
-      </c>
       <c r="V39" s="1">
         <v>0</v>
       </c>
@@ -3387,8 +3674,11 @@
       <c r="X39" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:24">
+      <c r="Y39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:32">
       <c r="C40" s="1">
         <v>20033</v>
       </c>
@@ -3399,13 +3689,13 @@
         <v>2003</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I40" s="1">
         <v>4</v>
@@ -3435,17 +3725,17 @@
         <v>0</v>
       </c>
       <c r="R40" s="1">
+        <v>0</v>
+      </c>
+      <c r="S40" s="1">
+        <v>0</v>
+      </c>
+      <c r="T40" s="1">
+        <v>0</v>
+      </c>
+      <c r="U40" s="1">
         <v>10</v>
       </c>
-      <c r="S40" s="1">
-        <v>0</v>
-      </c>
-      <c r="T40" s="1">
-        <v>0</v>
-      </c>
-      <c r="U40" s="1">
-        <v>0</v>
-      </c>
       <c r="V40" s="1">
         <v>0</v>
       </c>
@@ -3455,8 +3745,11 @@
       <c r="X40" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:24">
+      <c r="Y40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:32">
       <c r="C41" s="1">
         <v>20043</v>
       </c>
@@ -3467,13 +3760,13 @@
         <v>2004</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I41" s="1">
         <v>4</v>
@@ -3503,17 +3796,17 @@
         <v>0</v>
       </c>
       <c r="R41" s="1">
+        <v>0</v>
+      </c>
+      <c r="S41" s="1">
+        <v>0</v>
+      </c>
+      <c r="T41" s="1">
+        <v>0</v>
+      </c>
+      <c r="U41" s="1">
         <v>10</v>
       </c>
-      <c r="S41" s="1">
-        <v>0</v>
-      </c>
-      <c r="T41" s="1">
-        <v>0</v>
-      </c>
-      <c r="U41" s="1">
-        <v>0</v>
-      </c>
       <c r="V41" s="1">
         <v>0</v>
       </c>
@@ -3523,8 +3816,11 @@
       <c r="X41" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:24">
+      <c r="Y41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:32">
       <c r="C42" s="1">
         <v>20073</v>
       </c>
@@ -3535,13 +3831,13 @@
         <v>2007</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I42" s="1">
         <v>4</v>
@@ -3571,17 +3867,17 @@
         <v>0</v>
       </c>
       <c r="R42" s="1">
+        <v>0</v>
+      </c>
+      <c r="S42" s="1">
+        <v>0</v>
+      </c>
+      <c r="T42" s="1">
+        <v>0</v>
+      </c>
+      <c r="U42" s="1">
         <v>10</v>
       </c>
-      <c r="S42" s="1">
-        <v>0</v>
-      </c>
-      <c r="T42" s="1">
-        <v>0</v>
-      </c>
-      <c r="U42" s="1">
-        <v>0</v>
-      </c>
       <c r="V42" s="1">
         <v>0</v>
       </c>
@@ -3591,9 +3887,20 @@
       <c r="X42" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" s="2" customFormat="1" customHeight="1"/>
-    <row r="46" customHeight="1" spans="3:24">
+      <c r="Y42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:32">
+      <c r="Z44" s="1"/>
+      <c r="AA44" s="1"/>
+      <c r="AB44" s="1"/>
+      <c r="AC44" s="1"/>
+      <c r="AD44" s="1"/>
+      <c r="AE44" s="1"/>
+      <c r="AF44" s="1"/>
+    </row>
+    <row r="46" customHeight="1" spans="3:32">
       <c r="C46" s="1">
         <v>30011</v>
       </c>
@@ -3604,13 +3911,13 @@
         <v>3001</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="I46" s="1">
         <v>4</v>
@@ -3660,8 +3967,11 @@
       <c r="X46" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:24">
+      <c r="Y46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:32">
       <c r="C47" s="1">
         <v>30021</v>
       </c>
@@ -3672,13 +3982,13 @@
         <v>3002</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="I47" s="1">
         <v>4</v>
@@ -3728,8 +4038,11 @@
       <c r="X47" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:24">
+      <c r="Y47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:32">
       <c r="C48" s="1">
         <v>30031</v>
       </c>
@@ -3740,13 +4053,13 @@
         <v>3003</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="I48" s="1">
         <v>4</v>
@@ -3796,8 +4109,11 @@
       <c r="X48" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:24">
+      <c r="Y48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:25">
       <c r="C49" s="1">
         <v>30041</v>
       </c>
@@ -3808,13 +4124,13 @@
         <v>3004</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="I49" s="1">
         <v>4</v>
@@ -3864,8 +4180,11 @@
       <c r="X49" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:24">
+      <c r="Y49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:25">
       <c r="C50" s="1">
         <v>30071</v>
       </c>
@@ -3876,13 +4195,13 @@
         <v>3007</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="I50" s="1">
         <v>4</v>
@@ -3932,12 +4251,15 @@
       <c r="X50" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:24">
+      <c r="Y50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:25">
       <c r="F51" s="4"/>
-      <c r="V51" s="4"/>
-    </row>
-    <row r="52" customHeight="1" spans="3:24">
+      <c r="X51" s="4"/>
+    </row>
+    <row r="52" customHeight="1" spans="3:25">
       <c r="C52" s="1">
         <v>30022</v>
       </c>
@@ -3948,13 +4270,13 @@
         <v>3002</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I52" s="1">
         <v>4</v>
@@ -4004,8 +4326,11 @@
       <c r="X52" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:24">
+      <c r="Y52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:25">
       <c r="C53" s="1">
         <v>30032</v>
       </c>
@@ -4016,13 +4341,13 @@
         <v>3003</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I53" s="1">
         <v>4</v>
@@ -4072,8 +4397,11 @@
       <c r="X53" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:24">
+      <c r="Y53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:25">
       <c r="C54" s="1">
         <v>30042</v>
       </c>
@@ -4084,13 +4412,13 @@
         <v>3004</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I54" s="1">
         <v>4</v>
@@ -4140,8 +4468,11 @@
       <c r="X54" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:24">
+      <c r="Y54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:25">
       <c r="C55" s="1">
         <v>30052</v>
       </c>
@@ -4152,13 +4483,13 @@
         <v>3005</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I55" s="1">
         <v>4</v>
@@ -4208,8 +4539,11 @@
       <c r="X55" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:24">
+      <c r="Y55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:25">
       <c r="C56" s="1">
         <v>30062</v>
       </c>
@@ -4220,13 +4554,13 @@
         <v>3006</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I56" s="1">
         <v>4</v>
@@ -4276,8 +4610,11 @@
       <c r="X56" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:24">
+      <c r="Y56" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:25">
       <c r="C57" s="1">
         <v>30072</v>
       </c>
@@ -4288,13 +4625,13 @@
         <v>3007</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I57" s="1">
         <v>4</v>
@@ -4344,12 +4681,15 @@
       <c r="X57" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:24">
+      <c r="Y57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:25">
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
     </row>
-    <row r="59" customHeight="1" spans="3:24">
+    <row r="59" customHeight="1" spans="3:25">
       <c r="C59" s="1">
         <v>30023</v>
       </c>
@@ -4360,13 +4700,13 @@
         <v>3002</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I59" s="1">
         <v>4</v>
@@ -4396,17 +4736,17 @@
         <v>0</v>
       </c>
       <c r="R59" s="1">
+        <v>0</v>
+      </c>
+      <c r="S59" s="1">
+        <v>0</v>
+      </c>
+      <c r="T59" s="1">
+        <v>0</v>
+      </c>
+      <c r="U59" s="1">
         <v>10</v>
       </c>
-      <c r="S59" s="1">
-        <v>0</v>
-      </c>
-      <c r="T59" s="1">
-        <v>0</v>
-      </c>
-      <c r="U59" s="1">
-        <v>0</v>
-      </c>
       <c r="V59" s="1">
         <v>0</v>
       </c>
@@ -4416,8 +4756,11 @@
       <c r="X59" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" customHeight="1" spans="3:24">
+      <c r="Y59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:25">
       <c r="C60" s="1">
         <v>30033</v>
       </c>
@@ -4428,13 +4771,13 @@
         <v>3003</v>
       </c>
       <c r="F60" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G60" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="G60" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="H60" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I60" s="1">
         <v>4</v>
@@ -4464,17 +4807,17 @@
         <v>0</v>
       </c>
       <c r="R60" s="1">
+        <v>0</v>
+      </c>
+      <c r="S60" s="1">
+        <v>0</v>
+      </c>
+      <c r="T60" s="1">
+        <v>0</v>
+      </c>
+      <c r="U60" s="1">
         <v>10</v>
       </c>
-      <c r="S60" s="1">
-        <v>0</v>
-      </c>
-      <c r="T60" s="1">
-        <v>0</v>
-      </c>
-      <c r="U60" s="1">
-        <v>0</v>
-      </c>
       <c r="V60" s="1">
         <v>0</v>
       </c>
@@ -4484,8 +4827,11 @@
       <c r="X60" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:24">
+      <c r="Y60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:25">
       <c r="C61" s="1">
         <v>30073</v>
       </c>
@@ -4496,13 +4842,13 @@
         <v>3007</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="I61" s="1">
         <v>4</v>
@@ -4532,17 +4878,17 @@
         <v>0</v>
       </c>
       <c r="R61" s="1">
+        <v>0</v>
+      </c>
+      <c r="S61" s="1">
+        <v>0</v>
+      </c>
+      <c r="T61" s="1">
+        <v>0</v>
+      </c>
+      <c r="U61" s="1">
         <v>10</v>
       </c>
-      <c r="S61" s="1">
-        <v>0</v>
-      </c>
-      <c r="T61" s="1">
-        <v>0</v>
-      </c>
-      <c r="U61" s="1">
-        <v>0</v>
-      </c>
       <c r="V61" s="1">
         <v>0</v>
       </c>
@@ -4550,6 +4896,9 @@
         <v>0</v>
       </c>
       <c r="X61" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0">
+    <comment ref="O3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -79,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="0">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -101,7 +101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD4" authorId="1">
+    <comment ref="AG4" authorId="1">
       <text>
         <r>
           <rPr>
@@ -123,7 +123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE4" authorId="1">
+    <comment ref="AH4" authorId="1">
       <text>
         <r>
           <rPr>
@@ -145,7 +145,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF4" authorId="1">
+    <comment ref="AI4" authorId="1">
       <text>
         <r>
           <rPr>
@@ -174,7 +174,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="93">
+  <si>
+    <t>#</t>
+  </si>
   <si>
     <t>_ID</t>
   </si>
@@ -189,6 +192,15 @@
   </si>
   <si>
     <t>技能描述</t>
+  </si>
+  <si>
+    <t>EquipRate</t>
+  </si>
+  <si>
+    <t>StartQuality</t>
+  </si>
+  <si>
+    <t>EndQuality</t>
   </si>
   <si>
     <t>词条叠加数量</t>
@@ -619,12 +631,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1417,302 +1429,341 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:AF61"/>
+  <dimension ref="C1:AI61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
     <col min="7" max="7" width="12" style="1" customWidth="1"/>
     <col min="8" max="8" width="20.3333333333333" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5083333333333" style="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="11.3333333333333" style="1" customWidth="1"/>
-    <col min="15" max="15" width="8" style="1" customWidth="1"/>
-    <col min="16" max="16" width="7.75" style="1" customWidth="1"/>
-    <col min="17" max="17" width="10.375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="7.75" style="1" customWidth="1"/>
-    <col min="19" max="19" width="7.50833333333333" style="1" customWidth="1"/>
-    <col min="20" max="20" width="10.625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="11.25" style="1" customWidth="1"/>
-    <col min="22" max="22" width="10.625" style="1" customWidth="1"/>
-    <col min="23" max="23" width="12.625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="9.25" style="1" customWidth="1"/>
-    <col min="25" max="25" width="10.75" style="1" customWidth="1"/>
-    <col min="26" max="29" width="10.0833333333333" style="1" customWidth="1"/>
-    <col min="30" max="31" width="9" style="1" customWidth="1"/>
-    <col min="32" max="32" width="7.58333333333333" style="1" customWidth="1"/>
-    <col min="33" max="16384" width="9" style="1"/>
+    <col min="9" max="9" width="15.75" style="1" customWidth="1"/>
+    <col min="10" max="11" width="14.75" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="8.375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="10.375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="11.5083333333333" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9.5" style="1" customWidth="1"/>
+    <col min="17" max="17" width="11.3333333333333" style="1" customWidth="1"/>
+    <col min="18" max="18" width="8" style="1" customWidth="1"/>
+    <col min="19" max="19" width="7.75" style="1" customWidth="1"/>
+    <col min="20" max="20" width="10.375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="7.75" style="1" customWidth="1"/>
+    <col min="22" max="22" width="7.50833333333333" style="1" customWidth="1"/>
+    <col min="23" max="23" width="10.625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="11.25" style="1" customWidth="1"/>
+    <col min="25" max="25" width="10.625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="12.625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="9.25" style="1" customWidth="1"/>
+    <col min="28" max="28" width="10.75" style="1" customWidth="1"/>
+    <col min="29" max="32" width="10.0833333333333" style="1" customWidth="1"/>
+    <col min="33" max="34" width="9" style="1" customWidth="1"/>
+    <col min="35" max="35" width="7.58333333333333" style="1" customWidth="1"/>
+    <col min="36" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="1" customHeight="1" spans="3:35">
+      <c r="F1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:35">
+      <c r="F2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:35">
       <c r="C3" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AC3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AD3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE3" s="3"/>
-      <c r="AF3" s="3"/>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:32">
+        <v>27</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH3" s="3"/>
+      <c r="AI3" s="3"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:35">
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y4" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="AD4" s="3" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="AE4" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AF4" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:32">
+        <v>53</v>
+      </c>
+      <c r="AG4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AI4" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:35">
       <c r="C5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Z5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AA5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AB5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AC5" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AD5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AE5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AF5" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:32">
+        <v>59</v>
+      </c>
+      <c r="AG5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI5" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:35">
       <c r="C6" s="1">
         <v>10011</v>
       </c>
@@ -1723,25 +1774,25 @@
         <v>1001</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I6" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="J6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L6" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
@@ -1752,18 +1803,18 @@
       <c r="O6" s="1">
         <v>0</v>
       </c>
-      <c r="P6" s="4">
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+      <c r="S6" s="4">
         <v>100</v>
       </c>
-      <c r="Q6" s="1">
-        <v>0</v>
-      </c>
-      <c r="R6" s="1">
-        <v>0</v>
-      </c>
-      <c r="S6" s="1">
-        <v>0</v>
-      </c>
       <c r="T6" s="1">
         <v>0</v>
       </c>
@@ -1782,8 +1833,17 @@
       <c r="Y6" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:32">
+      <c r="Z6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:35">
       <c r="C7" s="1">
         <v>10021</v>
       </c>
@@ -1794,25 +1854,25 @@
         <v>1002</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I7" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="J7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L7" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M7" s="1">
         <v>0</v>
@@ -1823,18 +1883,18 @@
       <c r="O7" s="1">
         <v>0</v>
       </c>
-      <c r="P7" s="4">
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="4">
         <v>1000</v>
       </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-      <c r="R7" s="1">
-        <v>0</v>
-      </c>
-      <c r="S7" s="1">
-        <v>0</v>
-      </c>
       <c r="T7" s="1">
         <v>0</v>
       </c>
@@ -1853,8 +1913,17 @@
       <c r="Y7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:32">
+      <c r="Z7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:35">
       <c r="C8" s="1">
         <v>10031</v>
       </c>
@@ -1865,25 +1934,25 @@
         <v>1003</v>
       </c>
       <c r="F8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="H8" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I8" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="J8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L8" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M8" s="1">
         <v>0</v>
@@ -1894,18 +1963,18 @@
       <c r="O8" s="1">
         <v>0</v>
       </c>
-      <c r="P8" s="4">
+      <c r="P8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>0</v>
+      </c>
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+      <c r="S8" s="4">
         <v>800</v>
       </c>
-      <c r="Q8" s="1">
-        <v>0</v>
-      </c>
-      <c r="R8" s="1">
-        <v>0</v>
-      </c>
-      <c r="S8" s="1">
-        <v>0</v>
-      </c>
       <c r="T8" s="1">
         <v>0</v>
       </c>
@@ -1924,8 +1993,17 @@
       <c r="Y8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:32">
+      <c r="Z8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:35">
       <c r="C9" s="1">
         <v>10041</v>
       </c>
@@ -1936,25 +2014,25 @@
         <v>1004</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I9" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="J9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L9" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M9" s="1">
         <v>0</v>
@@ -1965,18 +2043,18 @@
       <c r="O9" s="1">
         <v>0</v>
       </c>
-      <c r="P9" s="4">
+      <c r="P9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+      <c r="S9" s="4">
         <v>2000</v>
       </c>
-      <c r="Q9" s="1">
-        <v>0</v>
-      </c>
-      <c r="R9" s="1">
-        <v>0</v>
-      </c>
-      <c r="S9" s="1">
-        <v>0</v>
-      </c>
       <c r="T9" s="1">
         <v>0</v>
       </c>
@@ -1995,8 +2073,17 @@
       <c r="Y9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:32">
+      <c r="Z9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:35">
       <c r="C10" s="1">
         <v>10071</v>
       </c>
@@ -2007,25 +2094,25 @@
         <v>1007</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I10" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="J10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L10" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M10" s="1">
         <v>0</v>
@@ -2036,18 +2123,18 @@
       <c r="O10" s="1">
         <v>0</v>
       </c>
-      <c r="P10" s="4">
+      <c r="P10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1">
+        <v>0</v>
+      </c>
+      <c r="S10" s="4">
         <v>10000</v>
       </c>
-      <c r="Q10" s="1">
-        <v>0</v>
-      </c>
-      <c r="R10" s="1">
-        <v>0</v>
-      </c>
-      <c r="S10" s="1">
-        <v>0</v>
-      </c>
       <c r="T10" s="1">
         <v>0</v>
       </c>
@@ -2066,21 +2153,30 @@
       <c r="Y10" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:32">
+      <c r="Z10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:35">
       <c r="F11" s="4"/>
-      <c r="R11" s="1">
-        <v>0</v>
-      </c>
-      <c r="S11" s="1">
-        <v>0</v>
-      </c>
-      <c r="T11" s="1">
-        <v>0</v>
-      </c>
-      <c r="X11" s="4"/>
-    </row>
-    <row r="12" customHeight="1" spans="3:32">
+      <c r="U11" s="1">
+        <v>0</v>
+      </c>
+      <c r="V11" s="1">
+        <v>0</v>
+      </c>
+      <c r="W11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="4"/>
+    </row>
+    <row r="12" customHeight="1" spans="3:35">
       <c r="C12" s="1">
         <v>10022</v>
       </c>
@@ -2091,25 +2187,25 @@
         <v>1002</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I12" s="1">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="J12" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K12" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L12" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M12" s="1">
         <v>0</v>
@@ -2123,18 +2219,18 @@
       <c r="P12" s="1">
         <v>0</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <v>0</v>
+      </c>
+      <c r="S12" s="1">
+        <v>0</v>
+      </c>
+      <c r="T12" s="4">
         <v>20</v>
       </c>
-      <c r="R12" s="1">
-        <v>0</v>
-      </c>
-      <c r="S12" s="1">
-        <v>0</v>
-      </c>
-      <c r="T12" s="1">
-        <v>0</v>
-      </c>
       <c r="U12" s="1">
         <v>0</v>
       </c>
@@ -2150,8 +2246,17 @@
       <c r="Y12" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:32">
+      <c r="Z12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:35">
       <c r="C13" s="1">
         <v>10032</v>
       </c>
@@ -2162,25 +2267,25 @@
         <v>1003</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I13" s="1">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="J13" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L13" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M13" s="1">
         <v>0</v>
@@ -2194,29 +2299,35 @@
       <c r="P13" s="1">
         <v>0</v>
       </c>
-      <c r="Q13" s="4">
+      <c r="Q13" s="1">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1">
+        <v>0</v>
+      </c>
+      <c r="S13" s="1">
+        <v>0</v>
+      </c>
+      <c r="T13" s="4">
         <v>10</v>
       </c>
-      <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
-      <c r="U13" s="1">
-        <v>0</v>
-      </c>
-      <c r="V13" s="1">
-        <v>0</v>
-      </c>
-      <c r="W13" s="1">
-        <v>0</v>
-      </c>
       <c r="X13" s="1">
         <v>0</v>
       </c>
       <c r="Y13" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:32">
+      <c r="Z13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:35">
       <c r="C14" s="1">
         <v>10042</v>
       </c>
@@ -2227,25 +2338,25 @@
         <v>1004</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I14" s="1">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="J14" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K14" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L14" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M14" s="1">
         <v>0</v>
@@ -2259,18 +2370,18 @@
       <c r="P14" s="1">
         <v>0</v>
       </c>
-      <c r="Q14" s="4">
+      <c r="Q14" s="1">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1">
+        <v>0</v>
+      </c>
+      <c r="S14" s="1">
+        <v>0</v>
+      </c>
+      <c r="T14" s="4">
         <v>30</v>
       </c>
-      <c r="R14" s="1">
-        <v>0</v>
-      </c>
-      <c r="S14" s="1">
-        <v>0</v>
-      </c>
-      <c r="T14" s="1">
-        <v>0</v>
-      </c>
       <c r="U14" s="1">
         <v>0</v>
       </c>
@@ -2286,8 +2397,17 @@
       <c r="Y14" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:32">
+      <c r="Z14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:35">
       <c r="C15" s="1">
         <v>10052</v>
       </c>
@@ -2298,25 +2418,25 @@
         <v>1005</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I15" s="1">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="J15" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K15" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L15" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M15" s="1">
         <v>0</v>
@@ -2327,20 +2447,20 @@
       <c r="O15" s="1">
         <v>0</v>
       </c>
-      <c r="P15" s="4">
+      <c r="P15" s="1">
         <v>0</v>
       </c>
       <c r="Q15" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R15" s="1">
         <v>0</v>
       </c>
-      <c r="S15" s="1">
+      <c r="S15" s="4">
         <v>0</v>
       </c>
       <c r="T15" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U15" s="1">
         <v>0</v>
@@ -2357,8 +2477,17 @@
       <c r="Y15" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:32">
+      <c r="Z15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:35">
       <c r="C16" s="1">
         <v>10062</v>
       </c>
@@ -2369,25 +2498,25 @@
         <v>1006</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I16" s="1">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="J16" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K16" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L16" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M16" s="1">
         <v>0</v>
@@ -2398,21 +2527,21 @@
       <c r="O16" s="1">
         <v>0</v>
       </c>
-      <c r="P16" s="4">
+      <c r="P16" s="1">
         <v>0</v>
       </c>
       <c r="Q16" s="1">
+        <v>0</v>
+      </c>
+      <c r="R16" s="1">
+        <v>0</v>
+      </c>
+      <c r="S16" s="4">
+        <v>0</v>
+      </c>
+      <c r="T16" s="1">
         <v>1</v>
       </c>
-      <c r="R16" s="1">
-        <v>0</v>
-      </c>
-      <c r="S16" s="1">
-        <v>0</v>
-      </c>
-      <c r="T16" s="1">
-        <v>0</v>
-      </c>
       <c r="U16" s="1">
         <v>0</v>
       </c>
@@ -2428,8 +2557,17 @@
       <c r="Y16" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:32">
+      <c r="Z16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:35">
       <c r="C17" s="1">
         <v>10072</v>
       </c>
@@ -2440,25 +2578,16 @@
         <v>1007</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I17" s="1">
-        <v>4</v>
-      </c>
-      <c r="J17" s="1">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="L17" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M17" s="1">
         <v>0</v>
@@ -2472,18 +2601,18 @@
       <c r="P17" s="1">
         <v>0</v>
       </c>
-      <c r="Q17" s="4">
+      <c r="Q17" s="1">
+        <v>0</v>
+      </c>
+      <c r="R17" s="1">
+        <v>0</v>
+      </c>
+      <c r="S17" s="1">
+        <v>0</v>
+      </c>
+      <c r="T17" s="4">
         <v>50</v>
       </c>
-      <c r="R17" s="1">
-        <v>0</v>
-      </c>
-      <c r="S17" s="1">
-        <v>0</v>
-      </c>
-      <c r="T17" s="1">
-        <v>0</v>
-      </c>
       <c r="U17" s="1">
         <v>0</v>
       </c>
@@ -2499,12 +2628,21 @@
       <c r="Y17" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:32">
+      <c r="Z17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:35">
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
     </row>
-    <row r="19" customHeight="1" spans="3:32">
+    <row r="19" customHeight="1" spans="3:35">
       <c r="C19" s="1">
         <v>10023</v>
       </c>
@@ -2515,25 +2653,25 @@
         <v>1002</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I19" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J19" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K19" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L19" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M19" s="1">
         <v>0</v>
@@ -2560,22 +2698,31 @@
         <v>0</v>
       </c>
       <c r="U19" s="1">
+        <v>0</v>
+      </c>
+      <c r="V19" s="1">
+        <v>0</v>
+      </c>
+      <c r="W19" s="1">
+        <v>0</v>
+      </c>
+      <c r="X19" s="1">
         <v>10</v>
       </c>
-      <c r="V19" s="1">
-        <v>0</v>
-      </c>
-      <c r="W19" s="1">
-        <v>0</v>
-      </c>
-      <c r="X19" s="1">
-        <v>0</v>
-      </c>
       <c r="Y19" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:32">
+      <c r="Z19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:35">
       <c r="C20" s="1">
         <v>10033</v>
       </c>
@@ -2586,25 +2733,25 @@
         <v>1003</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I20" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J20" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K20" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L20" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M20" s="1">
         <v>0</v>
@@ -2631,22 +2778,31 @@
         <v>0</v>
       </c>
       <c r="U20" s="1">
+        <v>0</v>
+      </c>
+      <c r="V20" s="1">
+        <v>0</v>
+      </c>
+      <c r="W20" s="1">
+        <v>0</v>
+      </c>
+      <c r="X20" s="1">
         <v>10</v>
       </c>
-      <c r="V20" s="1">
-        <v>0</v>
-      </c>
-      <c r="W20" s="1">
-        <v>0</v>
-      </c>
-      <c r="X20" s="1">
-        <v>0</v>
-      </c>
       <c r="Y20" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:32">
+      <c r="Z20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:35">
       <c r="C21" s="1">
         <v>10043</v>
       </c>
@@ -2657,25 +2813,25 @@
         <v>1004</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I21" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J21" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K21" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L21" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M21" s="1">
         <v>0</v>
@@ -2702,22 +2858,31 @@
         <v>0</v>
       </c>
       <c r="U21" s="1">
+        <v>0</v>
+      </c>
+      <c r="V21" s="1">
+        <v>0</v>
+      </c>
+      <c r="W21" s="1">
+        <v>0</v>
+      </c>
+      <c r="X21" s="1">
         <v>10</v>
       </c>
-      <c r="V21" s="1">
-        <v>0</v>
-      </c>
-      <c r="W21" s="1">
-        <v>0</v>
-      </c>
-      <c r="X21" s="1">
-        <v>0</v>
-      </c>
       <c r="Y21" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:32">
+      <c r="Z21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:35">
       <c r="C22" s="1">
         <v>10073</v>
       </c>
@@ -2728,25 +2893,25 @@
         <v>1007</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I22" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J22" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K22" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L22" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M22" s="1">
         <v>0</v>
@@ -2773,34 +2938,43 @@
         <v>0</v>
       </c>
       <c r="U22" s="1">
+        <v>0</v>
+      </c>
+      <c r="V22" s="1">
+        <v>0</v>
+      </c>
+      <c r="W22" s="1">
+        <v>0</v>
+      </c>
+      <c r="X22" s="1">
         <v>10</v>
       </c>
-      <c r="V22" s="1">
-        <v>0</v>
-      </c>
-      <c r="W22" s="1">
-        <v>0</v>
-      </c>
-      <c r="X22" s="1">
-        <v>0</v>
-      </c>
       <c r="Y22" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:32">
-      <c r="X23" s="4"/>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:32">
-      <c r="Z24" s="1"/>
-      <c r="AA24" s="1"/>
-      <c r="AB24" s="1"/>
+      <c r="Z22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:35">
+      <c r="AA23" s="4"/>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:35">
       <c r="AC24" s="1"/>
       <c r="AD24" s="1"/>
       <c r="AE24" s="1"/>
       <c r="AF24" s="1"/>
-    </row>
-    <row r="26" customHeight="1" spans="3:32">
+      <c r="AG24" s="1"/>
+      <c r="AH24" s="1"/>
+      <c r="AI24" s="1"/>
+    </row>
+    <row r="26" customHeight="1" spans="3:35">
       <c r="C26" s="1">
         <v>20011</v>
       </c>
@@ -2811,25 +2985,25 @@
         <v>2001</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I26" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="J26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L26" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M26" s="1">
         <v>0</v>
@@ -2840,18 +3014,18 @@
       <c r="O26" s="1">
         <v>0</v>
       </c>
-      <c r="P26" s="4">
+      <c r="P26" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>0</v>
+      </c>
+      <c r="R26" s="1">
+        <v>0</v>
+      </c>
+      <c r="S26" s="4">
         <v>100</v>
       </c>
-      <c r="Q26" s="1">
-        <v>0</v>
-      </c>
-      <c r="R26" s="1">
-        <v>0</v>
-      </c>
-      <c r="S26" s="1">
-        <v>0</v>
-      </c>
       <c r="T26" s="1">
         <v>0</v>
       </c>
@@ -2870,8 +3044,17 @@
       <c r="Y26" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:32">
+      <c r="Z26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:35">
       <c r="C27" s="1">
         <v>20021</v>
       </c>
@@ -2882,25 +3065,25 @@
         <v>2002</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I27" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="J27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L27" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M27" s="1">
         <v>0</v>
@@ -2911,18 +3094,18 @@
       <c r="O27" s="1">
         <v>0</v>
       </c>
-      <c r="P27" s="4">
+      <c r="P27" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>0</v>
+      </c>
+      <c r="R27" s="1">
+        <v>0</v>
+      </c>
+      <c r="S27" s="4">
         <v>1000</v>
       </c>
-      <c r="Q27" s="1">
-        <v>0</v>
-      </c>
-      <c r="R27" s="1">
-        <v>0</v>
-      </c>
-      <c r="S27" s="1">
-        <v>0</v>
-      </c>
       <c r="T27" s="1">
         <v>0</v>
       </c>
@@ -2941,8 +3124,17 @@
       <c r="Y27" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:32">
+      <c r="Z27" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:35">
       <c r="C28" s="1">
         <v>20031</v>
       </c>
@@ -2953,25 +3145,25 @@
         <v>2003</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I28" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="J28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L28" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M28" s="1">
         <v>0</v>
@@ -2982,18 +3174,18 @@
       <c r="O28" s="1">
         <v>0</v>
       </c>
-      <c r="P28" s="4">
+      <c r="P28" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>0</v>
+      </c>
+      <c r="R28" s="1">
+        <v>0</v>
+      </c>
+      <c r="S28" s="4">
         <v>800</v>
       </c>
-      <c r="Q28" s="1">
-        <v>0</v>
-      </c>
-      <c r="R28" s="1">
-        <v>0</v>
-      </c>
-      <c r="S28" s="1">
-        <v>0</v>
-      </c>
       <c r="T28" s="1">
         <v>0</v>
       </c>
@@ -3012,8 +3204,17 @@
       <c r="Y28" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:32">
+      <c r="Z28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:35">
       <c r="C29" s="1">
         <v>20041</v>
       </c>
@@ -3024,25 +3225,25 @@
         <v>2004</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I29" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="J29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L29" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M29" s="1">
         <v>0</v>
@@ -3053,18 +3254,18 @@
       <c r="O29" s="1">
         <v>0</v>
       </c>
-      <c r="P29" s="4">
+      <c r="P29" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>0</v>
+      </c>
+      <c r="R29" s="1">
+        <v>0</v>
+      </c>
+      <c r="S29" s="4">
         <v>2000</v>
       </c>
-      <c r="Q29" s="1">
-        <v>0</v>
-      </c>
-      <c r="R29" s="1">
-        <v>0</v>
-      </c>
-      <c r="S29" s="1">
-        <v>0</v>
-      </c>
       <c r="T29" s="1">
         <v>0</v>
       </c>
@@ -3083,8 +3284,17 @@
       <c r="Y29" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:32">
+      <c r="Z29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:35">
       <c r="C30" s="1">
         <v>20071</v>
       </c>
@@ -3095,25 +3305,25 @@
         <v>2007</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I30" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="J30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L30" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M30" s="1">
         <v>0</v>
@@ -3124,18 +3334,18 @@
       <c r="O30" s="1">
         <v>0</v>
       </c>
-      <c r="P30" s="4">
+      <c r="P30" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>0</v>
+      </c>
+      <c r="R30" s="1">
+        <v>0</v>
+      </c>
+      <c r="S30" s="4">
         <v>10000</v>
       </c>
-      <c r="Q30" s="1">
-        <v>0</v>
-      </c>
-      <c r="R30" s="1">
-        <v>0</v>
-      </c>
-      <c r="S30" s="1">
-        <v>0</v>
-      </c>
       <c r="T30" s="1">
         <v>0</v>
       </c>
@@ -3154,21 +3364,30 @@
       <c r="Y30" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:32">
+      <c r="Z30" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:35">
       <c r="F31" s="4"/>
-      <c r="R31" s="1">
-        <v>0</v>
-      </c>
-      <c r="S31" s="1">
-        <v>0</v>
-      </c>
-      <c r="T31" s="1">
-        <v>0</v>
-      </c>
-      <c r="X31" s="4"/>
-    </row>
-    <row r="32" customHeight="1" spans="3:32">
+      <c r="U31" s="1">
+        <v>0</v>
+      </c>
+      <c r="V31" s="1">
+        <v>0</v>
+      </c>
+      <c r="W31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="4"/>
+    </row>
+    <row r="32" customHeight="1" spans="3:35">
       <c r="C32" s="1">
         <v>20022</v>
       </c>
@@ -3179,25 +3398,25 @@
         <v>2002</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I32" s="1">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="J32" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K32" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L32" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M32" s="1">
         <v>0</v>
@@ -3211,18 +3430,18 @@
       <c r="P32" s="1">
         <v>0</v>
       </c>
-      <c r="Q32" s="4">
+      <c r="Q32" s="1">
+        <v>0</v>
+      </c>
+      <c r="R32" s="1">
+        <v>0</v>
+      </c>
+      <c r="S32" s="1">
+        <v>0</v>
+      </c>
+      <c r="T32" s="4">
         <v>20</v>
       </c>
-      <c r="R32" s="1">
-        <v>0</v>
-      </c>
-      <c r="S32" s="1">
-        <v>0</v>
-      </c>
-      <c r="T32" s="1">
-        <v>0</v>
-      </c>
       <c r="U32" s="1">
         <v>0</v>
       </c>
@@ -3238,8 +3457,17 @@
       <c r="Y32" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:32">
+      <c r="Z32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:35">
       <c r="C33" s="1">
         <v>20032</v>
       </c>
@@ -3250,25 +3478,25 @@
         <v>2003</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I33" s="1">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="J33" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K33" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L33" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M33" s="1">
         <v>0</v>
@@ -3282,18 +3510,18 @@
       <c r="P33" s="1">
         <v>0</v>
       </c>
-      <c r="Q33" s="4">
+      <c r="Q33" s="1">
+        <v>0</v>
+      </c>
+      <c r="R33" s="1">
+        <v>0</v>
+      </c>
+      <c r="S33" s="1">
+        <v>0</v>
+      </c>
+      <c r="T33" s="4">
         <v>10</v>
       </c>
-      <c r="R33" s="1">
-        <v>0</v>
-      </c>
-      <c r="S33" s="1">
-        <v>0</v>
-      </c>
-      <c r="T33" s="1">
-        <v>0</v>
-      </c>
       <c r="U33" s="1">
         <v>0</v>
       </c>
@@ -3309,8 +3537,17 @@
       <c r="Y33" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:32">
+      <c r="Z33" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:35">
       <c r="C34" s="1">
         <v>20042</v>
       </c>
@@ -3321,25 +3558,25 @@
         <v>2004</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I34" s="1">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="J34" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K34" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L34" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M34" s="1">
         <v>0</v>
@@ -3353,18 +3590,18 @@
       <c r="P34" s="1">
         <v>0</v>
       </c>
-      <c r="Q34" s="4">
+      <c r="Q34" s="1">
+        <v>0</v>
+      </c>
+      <c r="R34" s="1">
+        <v>0</v>
+      </c>
+      <c r="S34" s="1">
+        <v>0</v>
+      </c>
+      <c r="T34" s="4">
         <v>30</v>
       </c>
-      <c r="R34" s="1">
-        <v>0</v>
-      </c>
-      <c r="S34" s="1">
-        <v>0</v>
-      </c>
-      <c r="T34" s="1">
-        <v>0</v>
-      </c>
       <c r="U34" s="1">
         <v>0</v>
       </c>
@@ -3380,8 +3617,17 @@
       <c r="Y34" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:32">
+      <c r="Z34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:35">
       <c r="C35" s="1">
         <v>20052</v>
       </c>
@@ -3392,25 +3638,25 @@
         <v>2005</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I35" s="1">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="J35" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K35" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L35" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M35" s="1">
         <v>0</v>
@@ -3421,20 +3667,20 @@
       <c r="O35" s="1">
         <v>0</v>
       </c>
-      <c r="P35" s="4">
+      <c r="P35" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>0</v>
+      </c>
+      <c r="R35" s="1">
+        <v>0</v>
+      </c>
+      <c r="S35" s="4">
         <v>50</v>
       </c>
-      <c r="Q35" s="1">
-        <v>5</v>
-      </c>
-      <c r="R35" s="1">
-        <v>0</v>
-      </c>
-      <c r="S35" s="1">
-        <v>0</v>
-      </c>
       <c r="T35" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U35" s="1">
         <v>0</v>
@@ -3451,8 +3697,17 @@
       <c r="Y35" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:32">
+      <c r="Z35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:35">
       <c r="C36" s="1">
         <v>20062</v>
       </c>
@@ -3463,25 +3718,25 @@
         <v>2006</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I36" s="1">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="J36" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K36" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L36" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M36" s="1">
         <v>0</v>
@@ -3492,21 +3747,21 @@
       <c r="O36" s="1">
         <v>0</v>
       </c>
-      <c r="P36" s="4">
+      <c r="P36" s="1">
         <v>0</v>
       </c>
       <c r="Q36" s="1">
+        <v>0</v>
+      </c>
+      <c r="R36" s="1">
+        <v>0</v>
+      </c>
+      <c r="S36" s="4">
+        <v>0</v>
+      </c>
+      <c r="T36" s="1">
         <v>1</v>
       </c>
-      <c r="R36" s="1">
-        <v>0</v>
-      </c>
-      <c r="S36" s="1">
-        <v>0</v>
-      </c>
-      <c r="T36" s="1">
-        <v>0</v>
-      </c>
       <c r="U36" s="1">
         <v>0</v>
       </c>
@@ -3522,8 +3777,17 @@
       <c r="Y36" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:32">
+      <c r="Z36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:35">
       <c r="C37" s="1">
         <v>20072</v>
       </c>
@@ -3534,25 +3798,16 @@
         <v>2007</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I37" s="1">
-        <v>4</v>
-      </c>
-      <c r="J37" s="1">
-        <v>0</v>
-      </c>
-      <c r="K37" s="1">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="L37" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M37" s="1">
         <v>0</v>
@@ -3566,18 +3821,18 @@
       <c r="P37" s="1">
         <v>0</v>
       </c>
-      <c r="Q37" s="4">
+      <c r="Q37" s="1">
+        <v>0</v>
+      </c>
+      <c r="R37" s="1">
+        <v>0</v>
+      </c>
+      <c r="S37" s="1">
+        <v>0</v>
+      </c>
+      <c r="T37" s="4">
         <v>50</v>
       </c>
-      <c r="R37" s="1">
-        <v>0</v>
-      </c>
-      <c r="S37" s="1">
-        <v>0</v>
-      </c>
-      <c r="T37" s="1">
-        <v>0</v>
-      </c>
       <c r="U37" s="1">
         <v>0</v>
       </c>
@@ -3593,21 +3848,30 @@
       <c r="Y37" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:32">
+      <c r="Z37" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:35">
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
-      <c r="R38" s="1">
-        <v>0</v>
-      </c>
-      <c r="S38" s="1">
-        <v>0</v>
-      </c>
-      <c r="T38" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:32">
+      <c r="U38" s="1">
+        <v>0</v>
+      </c>
+      <c r="V38" s="1">
+        <v>0</v>
+      </c>
+      <c r="W38" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:35">
       <c r="C39" s="1">
         <v>20023</v>
       </c>
@@ -3618,25 +3882,25 @@
         <v>2002</v>
       </c>
       <c r="F39" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="H39" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I39" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J39" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K39" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L39" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M39" s="1">
         <v>0</v>
@@ -3663,22 +3927,31 @@
         <v>0</v>
       </c>
       <c r="U39" s="1">
+        <v>0</v>
+      </c>
+      <c r="V39" s="1">
+        <v>0</v>
+      </c>
+      <c r="W39" s="1">
+        <v>0</v>
+      </c>
+      <c r="X39" s="1">
         <v>10</v>
       </c>
-      <c r="V39" s="1">
-        <v>0</v>
-      </c>
-      <c r="W39" s="1">
-        <v>0</v>
-      </c>
-      <c r="X39" s="1">
-        <v>0</v>
-      </c>
       <c r="Y39" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:32">
+      <c r="Z39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:35">
       <c r="C40" s="1">
         <v>20033</v>
       </c>
@@ -3689,25 +3962,25 @@
         <v>2003</v>
       </c>
       <c r="F40" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H40" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="I40" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J40" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K40" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L40" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M40" s="1">
         <v>0</v>
@@ -3734,22 +4007,31 @@
         <v>0</v>
       </c>
       <c r="U40" s="1">
+        <v>0</v>
+      </c>
+      <c r="V40" s="1">
+        <v>0</v>
+      </c>
+      <c r="W40" s="1">
+        <v>0</v>
+      </c>
+      <c r="X40" s="1">
         <v>10</v>
       </c>
-      <c r="V40" s="1">
-        <v>0</v>
-      </c>
-      <c r="W40" s="1">
-        <v>0</v>
-      </c>
-      <c r="X40" s="1">
-        <v>0</v>
-      </c>
       <c r="Y40" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:32">
+      <c r="Z40" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:35">
       <c r="C41" s="1">
         <v>20043</v>
       </c>
@@ -3760,25 +4042,25 @@
         <v>2004</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I41" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J41" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K41" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L41" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M41" s="1">
         <v>0</v>
@@ -3805,22 +4087,31 @@
         <v>0</v>
       </c>
       <c r="U41" s="1">
+        <v>0</v>
+      </c>
+      <c r="V41" s="1">
+        <v>0</v>
+      </c>
+      <c r="W41" s="1">
+        <v>0</v>
+      </c>
+      <c r="X41" s="1">
         <v>10</v>
       </c>
-      <c r="V41" s="1">
-        <v>0</v>
-      </c>
-      <c r="W41" s="1">
-        <v>0</v>
-      </c>
-      <c r="X41" s="1">
-        <v>0</v>
-      </c>
       <c r="Y41" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:32">
+      <c r="Z41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:35">
       <c r="C42" s="1">
         <v>20073</v>
       </c>
@@ -3831,25 +4122,25 @@
         <v>2007</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I42" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J42" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K42" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L42" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M42" s="1">
         <v>0</v>
@@ -3876,31 +4167,40 @@
         <v>0</v>
       </c>
       <c r="U42" s="1">
+        <v>0</v>
+      </c>
+      <c r="V42" s="1">
+        <v>0</v>
+      </c>
+      <c r="W42" s="1">
+        <v>0</v>
+      </c>
+      <c r="X42" s="1">
         <v>10</v>
       </c>
-      <c r="V42" s="1">
-        <v>0</v>
-      </c>
-      <c r="W42" s="1">
-        <v>0</v>
-      </c>
-      <c r="X42" s="1">
-        <v>0</v>
-      </c>
       <c r="Y42" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:32">
-      <c r="Z44" s="1"/>
-      <c r="AA44" s="1"/>
-      <c r="AB44" s="1"/>
+      <c r="Z42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:35">
       <c r="AC44" s="1"/>
       <c r="AD44" s="1"/>
       <c r="AE44" s="1"/>
       <c r="AF44" s="1"/>
-    </row>
-    <row r="46" customHeight="1" spans="3:32">
+      <c r="AG44" s="1"/>
+      <c r="AH44" s="1"/>
+      <c r="AI44" s="1"/>
+    </row>
+    <row r="46" customHeight="1" spans="3:35">
       <c r="C46" s="1">
         <v>30011</v>
       </c>
@@ -3911,25 +4211,25 @@
         <v>3001</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I46" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="J46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L46" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M46" s="1">
         <v>0</v>
@@ -3940,18 +4240,18 @@
       <c r="O46" s="1">
         <v>0</v>
       </c>
-      <c r="P46" s="4">
+      <c r="P46" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>0</v>
+      </c>
+      <c r="R46" s="1">
+        <v>0</v>
+      </c>
+      <c r="S46" s="4">
         <v>100</v>
       </c>
-      <c r="Q46" s="1">
-        <v>0</v>
-      </c>
-      <c r="R46" s="1">
-        <v>0</v>
-      </c>
-      <c r="S46" s="1">
-        <v>0</v>
-      </c>
       <c r="T46" s="1">
         <v>0</v>
       </c>
@@ -3970,8 +4270,17 @@
       <c r="Y46" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:32">
+      <c r="Z46" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:35">
       <c r="C47" s="1">
         <v>30021</v>
       </c>
@@ -3982,25 +4291,25 @@
         <v>3002</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I47" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="J47" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L47" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M47" s="1">
         <v>0</v>
@@ -4011,18 +4320,18 @@
       <c r="O47" s="1">
         <v>0</v>
       </c>
-      <c r="P47" s="4">
+      <c r="P47" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="1">
+        <v>0</v>
+      </c>
+      <c r="R47" s="1">
+        <v>0</v>
+      </c>
+      <c r="S47" s="4">
         <v>1000</v>
       </c>
-      <c r="Q47" s="1">
-        <v>0</v>
-      </c>
-      <c r="R47" s="1">
-        <v>0</v>
-      </c>
-      <c r="S47" s="1">
-        <v>0</v>
-      </c>
       <c r="T47" s="1">
         <v>0</v>
       </c>
@@ -4041,8 +4350,17 @@
       <c r="Y47" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:32">
+      <c r="Z47" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:35">
       <c r="C48" s="1">
         <v>30031</v>
       </c>
@@ -4053,25 +4371,25 @@
         <v>3003</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I48" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="J48" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L48" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M48" s="1">
         <v>0</v>
@@ -4082,18 +4400,18 @@
       <c r="O48" s="1">
         <v>0</v>
       </c>
-      <c r="P48" s="4">
+      <c r="P48" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="1">
+        <v>0</v>
+      </c>
+      <c r="R48" s="1">
+        <v>0</v>
+      </c>
+      <c r="S48" s="4">
         <v>800</v>
       </c>
-      <c r="Q48" s="1">
-        <v>0</v>
-      </c>
-      <c r="R48" s="1">
-        <v>0</v>
-      </c>
-      <c r="S48" s="1">
-        <v>0</v>
-      </c>
       <c r="T48" s="1">
         <v>0</v>
       </c>
@@ -4112,8 +4430,17 @@
       <c r="Y48" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:25">
+      <c r="Z48" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:28">
       <c r="C49" s="1">
         <v>30041</v>
       </c>
@@ -4124,25 +4451,25 @@
         <v>3004</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="I49" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="J49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L49" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M49" s="1">
         <v>0</v>
@@ -4153,18 +4480,18 @@
       <c r="O49" s="1">
         <v>0</v>
       </c>
-      <c r="P49" s="4">
+      <c r="P49" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="1">
+        <v>0</v>
+      </c>
+      <c r="R49" s="1">
+        <v>0</v>
+      </c>
+      <c r="S49" s="4">
         <v>100000</v>
       </c>
-      <c r="Q49" s="1">
-        <v>0</v>
-      </c>
-      <c r="R49" s="1">
-        <v>0</v>
-      </c>
-      <c r="S49" s="1">
-        <v>0</v>
-      </c>
       <c r="T49" s="1">
         <v>0</v>
       </c>
@@ -4183,8 +4510,17 @@
       <c r="Y49" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:25">
+      <c r="Z49" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:28">
       <c r="C50" s="1">
         <v>30071</v>
       </c>
@@ -4195,25 +4531,25 @@
         <v>3007</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I50" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="J50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L50" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M50" s="1">
         <v>0</v>
@@ -4224,18 +4560,18 @@
       <c r="O50" s="1">
         <v>0</v>
       </c>
-      <c r="P50" s="4">
+      <c r="P50" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="1">
+        <v>0</v>
+      </c>
+      <c r="R50" s="1">
+        <v>0</v>
+      </c>
+      <c r="S50" s="4">
         <v>10000</v>
       </c>
-      <c r="Q50" s="1">
-        <v>0</v>
-      </c>
-      <c r="R50" s="1">
-        <v>0</v>
-      </c>
-      <c r="S50" s="1">
-        <v>0</v>
-      </c>
       <c r="T50" s="1">
         <v>0</v>
       </c>
@@ -4254,12 +4590,21 @@
       <c r="Y50" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:25">
+      <c r="Z50" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:28">
       <c r="F51" s="4"/>
-      <c r="X51" s="4"/>
-    </row>
-    <row r="52" customHeight="1" spans="3:25">
+      <c r="AA51" s="4"/>
+    </row>
+    <row r="52" customHeight="1" spans="3:28">
       <c r="C52" s="1">
         <v>30022</v>
       </c>
@@ -4270,25 +4615,25 @@
         <v>3002</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I52" s="1">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="J52" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K52" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L52" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M52" s="1">
         <v>0</v>
@@ -4302,18 +4647,18 @@
       <c r="P52" s="1">
         <v>0</v>
       </c>
-      <c r="Q52" s="4">
+      <c r="Q52" s="1">
+        <v>0</v>
+      </c>
+      <c r="R52" s="1">
+        <v>0</v>
+      </c>
+      <c r="S52" s="1">
+        <v>0</v>
+      </c>
+      <c r="T52" s="4">
         <v>20</v>
       </c>
-      <c r="R52" s="1">
-        <v>0</v>
-      </c>
-      <c r="S52" s="1">
-        <v>0</v>
-      </c>
-      <c r="T52" s="1">
-        <v>0</v>
-      </c>
       <c r="U52" s="1">
         <v>0</v>
       </c>
@@ -4329,8 +4674,17 @@
       <c r="Y52" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:25">
+      <c r="Z52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:28">
       <c r="C53" s="1">
         <v>30032</v>
       </c>
@@ -4341,25 +4695,25 @@
         <v>3003</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I53" s="1">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="J53" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K53" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L53" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M53" s="1">
         <v>0</v>
@@ -4373,18 +4727,18 @@
       <c r="P53" s="1">
         <v>0</v>
       </c>
-      <c r="Q53" s="4">
+      <c r="Q53" s="1">
+        <v>0</v>
+      </c>
+      <c r="R53" s="1">
+        <v>0</v>
+      </c>
+      <c r="S53" s="1">
+        <v>0</v>
+      </c>
+      <c r="T53" s="4">
         <v>10</v>
       </c>
-      <c r="R53" s="1">
-        <v>0</v>
-      </c>
-      <c r="S53" s="1">
-        <v>0</v>
-      </c>
-      <c r="T53" s="1">
-        <v>0</v>
-      </c>
       <c r="U53" s="1">
         <v>0</v>
       </c>
@@ -4400,8 +4754,17 @@
       <c r="Y53" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:25">
+      <c r="Z53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:28">
       <c r="C54" s="1">
         <v>30042</v>
       </c>
@@ -4412,25 +4775,25 @@
         <v>3004</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I54" s="1">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="J54" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K54" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L54" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M54" s="1">
         <v>0</v>
@@ -4444,18 +4807,18 @@
       <c r="P54" s="1">
         <v>0</v>
       </c>
-      <c r="Q54" s="4">
+      <c r="Q54" s="1">
+        <v>0</v>
+      </c>
+      <c r="R54" s="1">
+        <v>0</v>
+      </c>
+      <c r="S54" s="1">
+        <v>0</v>
+      </c>
+      <c r="T54" s="4">
         <v>100</v>
       </c>
-      <c r="R54" s="1">
-        <v>0</v>
-      </c>
-      <c r="S54" s="1">
-        <v>0</v>
-      </c>
-      <c r="T54" s="1">
-        <v>0</v>
-      </c>
       <c r="U54" s="1">
         <v>0</v>
       </c>
@@ -4471,8 +4834,17 @@
       <c r="Y54" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:25">
+      <c r="Z54" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:28">
       <c r="C55" s="1">
         <v>30052</v>
       </c>
@@ -4483,25 +4855,25 @@
         <v>3005</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I55" s="1">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="J55" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K55" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L55" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M55" s="1">
         <v>0</v>
@@ -4512,20 +4884,20 @@
       <c r="O55" s="1">
         <v>0</v>
       </c>
-      <c r="P55" s="4">
+      <c r="P55" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="1">
+        <v>0</v>
+      </c>
+      <c r="R55" s="1">
+        <v>0</v>
+      </c>
+      <c r="S55" s="4">
         <v>50</v>
       </c>
-      <c r="Q55" s="1">
-        <v>5</v>
-      </c>
-      <c r="R55" s="1">
-        <v>0</v>
-      </c>
-      <c r="S55" s="1">
-        <v>0</v>
-      </c>
       <c r="T55" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U55" s="1">
         <v>0</v>
@@ -4542,8 +4914,17 @@
       <c r="Y55" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:25">
+      <c r="Z55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:28">
       <c r="C56" s="1">
         <v>30062</v>
       </c>
@@ -4554,25 +4935,25 @@
         <v>3006</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I56" s="1">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="J56" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K56" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L56" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M56" s="1">
         <v>0</v>
@@ -4583,21 +4964,21 @@
       <c r="O56" s="1">
         <v>0</v>
       </c>
-      <c r="P56" s="4">
+      <c r="P56" s="1">
         <v>0</v>
       </c>
       <c r="Q56" s="1">
+        <v>0</v>
+      </c>
+      <c r="R56" s="1">
+        <v>0</v>
+      </c>
+      <c r="S56" s="4">
+        <v>0</v>
+      </c>
+      <c r="T56" s="1">
         <v>1</v>
       </c>
-      <c r="R56" s="1">
-        <v>0</v>
-      </c>
-      <c r="S56" s="1">
-        <v>0</v>
-      </c>
-      <c r="T56" s="1">
-        <v>0</v>
-      </c>
       <c r="U56" s="1">
         <v>0</v>
       </c>
@@ -4613,8 +4994,17 @@
       <c r="Y56" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:25">
+      <c r="Z56" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA56" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB56" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:28">
       <c r="C57" s="1">
         <v>30072</v>
       </c>
@@ -4625,25 +5015,25 @@
         <v>3007</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I57" s="1">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="J57" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K57" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L57" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M57" s="1">
         <v>0</v>
@@ -4657,18 +5047,18 @@
       <c r="P57" s="1">
         <v>0</v>
       </c>
-      <c r="Q57" s="4">
+      <c r="Q57" s="1">
+        <v>0</v>
+      </c>
+      <c r="R57" s="1">
+        <v>0</v>
+      </c>
+      <c r="S57" s="1">
+        <v>0</v>
+      </c>
+      <c r="T57" s="4">
         <v>50</v>
       </c>
-      <c r="R57" s="1">
-        <v>0</v>
-      </c>
-      <c r="S57" s="1">
-        <v>0</v>
-      </c>
-      <c r="T57" s="1">
-        <v>0</v>
-      </c>
       <c r="U57" s="1">
         <v>0</v>
       </c>
@@ -4684,12 +5074,21 @@
       <c r="Y57" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:25">
+      <c r="Z57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:28">
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
     </row>
-    <row r="59" customHeight="1" spans="3:25">
+    <row r="59" customHeight="1" spans="3:28">
       <c r="C59" s="1">
         <v>30023</v>
       </c>
@@ -4700,25 +5099,25 @@
         <v>3002</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I59" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J59" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K59" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L59" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M59" s="1">
         <v>0</v>
@@ -4745,22 +5144,31 @@
         <v>0</v>
       </c>
       <c r="U59" s="1">
+        <v>0</v>
+      </c>
+      <c r="V59" s="1">
+        <v>0</v>
+      </c>
+      <c r="W59" s="1">
+        <v>0</v>
+      </c>
+      <c r="X59" s="1">
         <v>10</v>
       </c>
-      <c r="V59" s="1">
-        <v>0</v>
-      </c>
-      <c r="W59" s="1">
-        <v>0</v>
-      </c>
-      <c r="X59" s="1">
-        <v>0</v>
-      </c>
       <c r="Y59" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" customHeight="1" spans="3:25">
+      <c r="Z59" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:28">
       <c r="C60" s="1">
         <v>30033</v>
       </c>
@@ -4771,25 +5179,25 @@
         <v>3003</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I60" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J60" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K60" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L60" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M60" s="1">
         <v>0</v>
@@ -4816,22 +5224,31 @@
         <v>0</v>
       </c>
       <c r="U60" s="1">
+        <v>0</v>
+      </c>
+      <c r="V60" s="1">
+        <v>0</v>
+      </c>
+      <c r="W60" s="1">
+        <v>0</v>
+      </c>
+      <c r="X60" s="1">
         <v>10</v>
       </c>
-      <c r="V60" s="1">
-        <v>0</v>
-      </c>
-      <c r="W60" s="1">
-        <v>0</v>
-      </c>
-      <c r="X60" s="1">
-        <v>0</v>
-      </c>
       <c r="Y60" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:25">
+      <c r="Z60" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:28">
       <c r="C61" s="1">
         <v>30073</v>
       </c>
@@ -4842,25 +5259,25 @@
         <v>3007</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="I61" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J61" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K61" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L61" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M61" s="1">
         <v>0</v>
@@ -4887,24 +5304,33 @@
         <v>0</v>
       </c>
       <c r="U61" s="1">
+        <v>0</v>
+      </c>
+      <c r="V61" s="1">
+        <v>0</v>
+      </c>
+      <c r="W61" s="1">
+        <v>0</v>
+      </c>
+      <c r="X61" s="1">
         <v>10</v>
       </c>
-      <c r="V61" s="1">
-        <v>0</v>
-      </c>
-      <c r="W61" s="1">
-        <v>0</v>
-      </c>
-      <c r="X61" s="1">
-        <v>0</v>
-      </c>
       <c r="Y61" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="1">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5 L3:M5 I3:K5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -4205,7 +4205,7 @@
         <v>30011</v>
       </c>
       <c r="D46" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E46" s="4">
         <v>3001</v>
@@ -4285,7 +4285,7 @@
         <v>30021</v>
       </c>
       <c r="D47" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E47" s="4">
         <v>3002</v>
@@ -4365,7 +4365,7 @@
         <v>30031</v>
       </c>
       <c r="D48" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E48" s="4">
         <v>3003</v>
@@ -4445,7 +4445,7 @@
         <v>30041</v>
       </c>
       <c r="D49" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E49" s="4">
         <v>3004</v>
@@ -4525,7 +4525,7 @@
         <v>30071</v>
       </c>
       <c r="D50" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E50" s="4">
         <v>3007</v>
@@ -4609,7 +4609,7 @@
         <v>30022</v>
       </c>
       <c r="D52" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E52" s="4">
         <v>3002</v>
@@ -4689,7 +4689,7 @@
         <v>30032</v>
       </c>
       <c r="D53" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E53" s="4">
         <v>3003</v>
@@ -4769,7 +4769,7 @@
         <v>30042</v>
       </c>
       <c r="D54" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E54" s="4">
         <v>3004</v>
@@ -4849,7 +4849,7 @@
         <v>30052</v>
       </c>
       <c r="D55" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E55" s="4">
         <v>3005</v>
@@ -4929,7 +4929,7 @@
         <v>30062</v>
       </c>
       <c r="D56" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E56" s="4">
         <v>3006</v>
@@ -5009,7 +5009,7 @@
         <v>30072</v>
       </c>
       <c r="D57" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E57" s="4">
         <v>3007</v>
@@ -5093,7 +5093,7 @@
         <v>30023</v>
       </c>
       <c r="D59" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59" s="4">
         <v>3002</v>
@@ -5173,7 +5173,7 @@
         <v>30033</v>
       </c>
       <c r="D60" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E60" s="4">
         <v>3003</v>
@@ -5253,7 +5253,7 @@
         <v>30073</v>
       </c>
       <c r="D61" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E61" s="4">
         <v>3007</v>
@@ -5330,7 +5330,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5 L3:M5 I3:K5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:M5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -174,7 +174,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="95">
   <si>
     <t>#</t>
   </si>
@@ -386,7 +386,13 @@
     <t>增加{1}%技能系数</t>
   </si>
   <si>
-    <t>武神盾</t>
+    <t>龙魂护体</t>
+  </si>
+  <si>
+    <t>·百重</t>
+  </si>
+  <si>
+    <t>增加{1}%的护盾值</t>
   </si>
   <si>
     <t>无求易决</t>
@@ -416,7 +422,7 @@
     <t>冰封术</t>
   </si>
   <si>
-    <t>念力盾</t>
+    <t>炎凰法盾</t>
   </si>
   <si>
     <t>冰心诀</t>
@@ -446,7 +452,7 @@
     <t>增加{0}点神兽攻击</t>
   </si>
   <si>
-    <t>护魂盾</t>
+    <t>太虚麟盾</t>
   </si>
   <si>
     <t>圣心诀</t>
@@ -2421,10 +2427,10 @@
         <v>70</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I15" s="1">
         <v>60</v>
@@ -2498,7 +2504,7 @@
         <v>1006</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>68</v>
@@ -2656,10 +2662,10 @@
         <v>63</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I19" s="1">
         <v>20</v>
@@ -2736,10 +2742,10 @@
         <v>65</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I20" s="1">
         <v>20</v>
@@ -2816,10 +2822,10 @@
         <v>66</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I21" s="1">
         <v>20</v>
@@ -2896,10 +2902,10 @@
         <v>67</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I22" s="1">
         <v>20</v>
@@ -2985,13 +2991,13 @@
         <v>2001</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I26" s="1">
         <v>100</v>
@@ -3065,7 +3071,7 @@
         <v>2002</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>61</v>
@@ -3145,7 +3151,7 @@
         <v>2003</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>61</v>
@@ -3225,7 +3231,7 @@
         <v>2004</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>61</v>
@@ -3305,7 +3311,7 @@
         <v>2007</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>61</v>
@@ -3398,7 +3404,7 @@
         <v>2002</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>68</v>
@@ -3478,7 +3484,7 @@
         <v>2003</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>68</v>
@@ -3558,7 +3564,7 @@
         <v>2004</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>68</v>
@@ -3638,13 +3644,13 @@
         <v>2005</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I35" s="1">
         <v>60</v>
@@ -3718,7 +3724,7 @@
         <v>2006</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>68</v>
@@ -3798,7 +3804,7 @@
         <v>2007</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>68</v>
@@ -3882,13 +3888,13 @@
         <v>2002</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I39" s="1">
         <v>20</v>
@@ -3962,13 +3968,13 @@
         <v>2003</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I40" s="1">
         <v>20</v>
@@ -4042,13 +4048,13 @@
         <v>2004</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I41" s="1">
         <v>20</v>
@@ -4122,13 +4128,13 @@
         <v>2007</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I42" s="1">
         <v>20</v>
@@ -4211,13 +4217,13 @@
         <v>3001</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I46" s="1">
         <v>100</v>
@@ -4291,7 +4297,7 @@
         <v>3002</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>61</v>
@@ -4371,7 +4377,7 @@
         <v>3003</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>61</v>
@@ -4451,13 +4457,13 @@
         <v>3004</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I49" s="1">
         <v>100</v>
@@ -4531,13 +4537,13 @@
         <v>3007</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I50" s="1">
         <v>100</v>
@@ -4615,7 +4621,7 @@
         <v>3002</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>68</v>
@@ -4695,7 +4701,7 @@
         <v>3003</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>68</v>
@@ -4775,7 +4781,7 @@
         <v>3004</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>68</v>
@@ -4855,13 +4861,13 @@
         <v>3005</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I55" s="1">
         <v>60</v>
@@ -4935,7 +4941,7 @@
         <v>3006</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>68</v>
@@ -5015,7 +5021,7 @@
         <v>3007</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>68</v>
@@ -5099,13 +5105,13 @@
         <v>3002</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I59" s="1">
         <v>20</v>
@@ -5179,13 +5185,13 @@
         <v>3003</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I60" s="1">
         <v>20</v>
@@ -5259,13 +5265,13 @@
         <v>3007</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I61" s="1">
         <v>20</v>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -4496,7 +4496,7 @@
         <v>0</v>
       </c>
       <c r="S49" s="4">
-        <v>100000</v>
+        <v>30000</v>
       </c>
       <c r="T49" s="1">
         <v>0</v>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O3" authorId="0">
+    <comment ref="Q3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -79,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0">
+    <comment ref="V3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -101,7 +101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG4" authorId="1">
+    <comment ref="AI4" authorId="1">
       <text>
         <r>
           <rPr>
@@ -123,7 +123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH4" authorId="1">
+    <comment ref="AJ4" authorId="1">
       <text>
         <r>
           <rPr>
@@ -145,7 +145,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI4" authorId="1">
+    <comment ref="AK4" authorId="1">
       <text>
         <r>
           <rPr>
@@ -174,7 +174,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="97">
   <si>
     <t>#</t>
   </si>
@@ -201,6 +201,12 @@
   </si>
   <si>
     <t>EndQuality</t>
+  </si>
+  <si>
+    <t>StartLevel</t>
+  </si>
+  <si>
+    <t>EndLevel</t>
   </si>
   <si>
     <t>词条叠加数量</t>
@@ -637,12 +643,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1435,48 +1441,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AI61"/>
+  <dimension ref="C1:AL61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
     <col min="7" max="7" width="12" style="1" customWidth="1"/>
     <col min="8" max="8" width="20.3333333333333" style="1" customWidth="1"/>
     <col min="9" max="9" width="15.75" style="1" customWidth="1"/>
-    <col min="10" max="11" width="14.75" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="8.375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.75" style="1" customWidth="1"/>
+    <col min="11" max="13" width="10.5" style="1" customWidth="1"/>
     <col min="14" max="14" width="10.375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="11.5083333333333" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9.5" style="1" customWidth="1"/>
-    <col min="17" max="17" width="11.3333333333333" style="1" customWidth="1"/>
-    <col min="18" max="18" width="8" style="1" customWidth="1"/>
-    <col min="19" max="19" width="7.75" style="1" customWidth="1"/>
-    <col min="20" max="20" width="10.375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="8.375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="10.375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="11.5083333333333" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.5" style="1" customWidth="1"/>
+    <col min="19" max="19" width="11.3333333333333" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8" style="1" customWidth="1"/>
     <col min="21" max="21" width="7.75" style="1" customWidth="1"/>
-    <col min="22" max="22" width="7.50833333333333" style="1" customWidth="1"/>
-    <col min="23" max="23" width="10.625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="11.25" style="1" customWidth="1"/>
+    <col min="22" max="22" width="10.375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="7.75" style="1" customWidth="1"/>
+    <col min="24" max="24" width="7.50833333333333" style="1" customWidth="1"/>
     <col min="25" max="25" width="10.625" style="1" customWidth="1"/>
-    <col min="26" max="26" width="12.625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="9.25" style="1" customWidth="1"/>
-    <col min="28" max="28" width="10.75" style="1" customWidth="1"/>
-    <col min="29" max="32" width="10.0833333333333" style="1" customWidth="1"/>
-    <col min="33" max="34" width="9" style="1" customWidth="1"/>
-    <col min="35" max="35" width="7.58333333333333" style="1" customWidth="1"/>
-    <col min="36" max="16384" width="9" style="1"/>
+    <col min="26" max="26" width="11.25" style="1" customWidth="1"/>
+    <col min="27" max="27" width="10.625" style="1" customWidth="1"/>
+    <col min="28" max="28" width="12.625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="9.25" style="1" customWidth="1"/>
+    <col min="30" max="30" width="10.75" style="1" customWidth="1"/>
+    <col min="31" max="34" width="10.0833333333333" style="1" customWidth="1"/>
+    <col min="35" max="36" width="9" style="1" customWidth="1"/>
+    <col min="37" max="37" width="7.58333333333333" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:35">
+    <row r="1" customHeight="1" spans="3:37">
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="3:35">
+    <row r="2" customHeight="1" spans="3:37">
       <c r="F2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:37">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1568,25 +1575,31 @@
       <c r="AG3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AH3" s="3"/>
-      <c r="AI3" s="3"/>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:35">
+      <c r="AH3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ3" s="3"/>
+      <c r="AK3" s="3"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:37">
       <c r="C4" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>6</v>
@@ -1598,10 +1611,10 @@
         <v>8</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>37</v>
@@ -1649,16 +1662,16 @@
         <v>51</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="AD4" s="3" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="AE4" s="3" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="AF4" s="3" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="AG4" s="3" t="s">
         <v>54</v>
@@ -1669,107 +1682,119 @@
       <c r="AI4" s="3" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:35">
+      <c r="AJ4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AK4" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:37">
       <c r="C5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AA5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AB5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AC5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AD5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AE5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AF5" s="3" t="s">
         <v>59</v>
       </c>
       <c r="AG5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AH5" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="AI5" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:35">
+        <v>59</v>
+      </c>
+      <c r="AJ5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AK5" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:37">
       <c r="C6" s="1">
         <v>10011</v>
       </c>
@@ -1780,13 +1805,13 @@
         <v>1001</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I6" s="1">
         <v>100</v>
@@ -1798,13 +1823,13 @@
         <v>5</v>
       </c>
       <c r="L6" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N6" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -1818,15 +1843,15 @@
       <c r="R6" s="1">
         <v>0</v>
       </c>
-      <c r="S6" s="4">
+      <c r="S6" s="1">
+        <v>0</v>
+      </c>
+      <c r="T6" s="1">
+        <v>0</v>
+      </c>
+      <c r="U6" s="4">
         <v>100</v>
       </c>
-      <c r="T6" s="1">
-        <v>0</v>
-      </c>
-      <c r="U6" s="1">
-        <v>0</v>
-      </c>
       <c r="V6" s="1">
         <v>0</v>
       </c>
@@ -1848,8 +1873,14 @@
       <c r="AB6" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:35">
+      <c r="AC6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:37">
       <c r="C7" s="1">
         <v>10021</v>
       </c>
@@ -1860,16 +1891,16 @@
         <v>1002</v>
       </c>
       <c r="F7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="H7" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I7" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J7" s="1">
         <v>1</v>
@@ -1878,13 +1909,13 @@
         <v>5</v>
       </c>
       <c r="L7" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M7" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N7" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -1898,15 +1929,15 @@
       <c r="R7" s="1">
         <v>0</v>
       </c>
-      <c r="S7" s="4">
+      <c r="S7" s="1">
+        <v>0</v>
+      </c>
+      <c r="T7" s="1">
+        <v>0</v>
+      </c>
+      <c r="U7" s="4">
         <v>1000</v>
       </c>
-      <c r="T7" s="1">
-        <v>0</v>
-      </c>
-      <c r="U7" s="1">
-        <v>0</v>
-      </c>
       <c r="V7" s="1">
         <v>0</v>
       </c>
@@ -1928,8 +1959,14 @@
       <c r="AB7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:35">
+      <c r="AC7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:37">
       <c r="C8" s="1">
         <v>10031</v>
       </c>
@@ -1940,16 +1977,16 @@
         <v>1003</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I8" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J8" s="1">
         <v>1</v>
@@ -1958,13 +1995,13 @@
         <v>5</v>
       </c>
       <c r="L8" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M8" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N8" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O8" s="1">
         <v>0</v>
@@ -1978,15 +2015,15 @@
       <c r="R8" s="1">
         <v>0</v>
       </c>
-      <c r="S8" s="4">
+      <c r="S8" s="1">
+        <v>0</v>
+      </c>
+      <c r="T8" s="1">
+        <v>0</v>
+      </c>
+      <c r="U8" s="4">
         <v>800</v>
       </c>
-      <c r="T8" s="1">
-        <v>0</v>
-      </c>
-      <c r="U8" s="1">
-        <v>0</v>
-      </c>
       <c r="V8" s="1">
         <v>0</v>
       </c>
@@ -2008,8 +2045,14 @@
       <c r="AB8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:35">
+      <c r="AC8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:37">
       <c r="C9" s="1">
         <v>10041</v>
       </c>
@@ -2020,16 +2063,16 @@
         <v>1004</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="I9" s="1">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="J9" s="1">
         <v>1</v>
@@ -2038,13 +2081,13 @@
         <v>5</v>
       </c>
       <c r="L9" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M9" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N9" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -2058,15 +2101,15 @@
       <c r="R9" s="1">
         <v>0</v>
       </c>
-      <c r="S9" s="4">
+      <c r="S9" s="1">
+        <v>0</v>
+      </c>
+      <c r="T9" s="1">
+        <v>0</v>
+      </c>
+      <c r="U9" s="4">
         <v>2000</v>
       </c>
-      <c r="T9" s="1">
-        <v>0</v>
-      </c>
-      <c r="U9" s="1">
-        <v>0</v>
-      </c>
       <c r="V9" s="1">
         <v>0</v>
       </c>
@@ -2088,8 +2131,14 @@
       <c r="AB9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:35">
+      <c r="AC9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:37">
       <c r="C10" s="1">
         <v>10071</v>
       </c>
@@ -2100,16 +2149,16 @@
         <v>1007</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I10" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="J10" s="1">
         <v>1</v>
@@ -2118,13 +2167,13 @@
         <v>5</v>
       </c>
       <c r="L10" s="1">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="M10" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N10" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O10" s="1">
         <v>0</v>
@@ -2138,15 +2187,15 @@
       <c r="R10" s="1">
         <v>0</v>
       </c>
-      <c r="S10" s="4">
+      <c r="S10" s="1">
+        <v>0</v>
+      </c>
+      <c r="T10" s="1">
+        <v>0</v>
+      </c>
+      <c r="U10" s="4">
         <v>10000</v>
       </c>
-      <c r="T10" s="1">
-        <v>0</v>
-      </c>
-      <c r="U10" s="1">
-        <v>0</v>
-      </c>
       <c r="V10" s="1">
         <v>0</v>
       </c>
@@ -2168,21 +2217,27 @@
       <c r="AB10" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:35">
+      <c r="AC10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:37">
       <c r="F11" s="4"/>
-      <c r="U11" s="1">
-        <v>0</v>
-      </c>
-      <c r="V11" s="1">
-        <v>0</v>
-      </c>
       <c r="W11" s="1">
         <v>0</v>
       </c>
-      <c r="AA11" s="4"/>
-    </row>
-    <row r="12" customHeight="1" spans="3:35">
+      <c r="X11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="4"/>
+    </row>
+    <row r="12" customHeight="1" spans="3:37">
       <c r="C12" s="1">
         <v>10022</v>
       </c>
@@ -2193,13 +2248,13 @@
         <v>1002</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I12" s="1">
         <v>60</v>
@@ -2211,13 +2266,13 @@
         <v>5</v>
       </c>
       <c r="L12" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M12" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N12" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O12" s="1">
         <v>0</v>
@@ -2234,15 +2289,15 @@
       <c r="S12" s="1">
         <v>0</v>
       </c>
-      <c r="T12" s="4">
+      <c r="T12" s="1">
+        <v>0</v>
+      </c>
+      <c r="U12" s="1">
+        <v>0</v>
+      </c>
+      <c r="V12" s="4">
         <v>20</v>
       </c>
-      <c r="U12" s="1">
-        <v>0</v>
-      </c>
-      <c r="V12" s="1">
-        <v>0</v>
-      </c>
       <c r="W12" s="1">
         <v>0</v>
       </c>
@@ -2261,8 +2316,14 @@
       <c r="AB12" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:35">
+      <c r="AC12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:37">
       <c r="C13" s="1">
         <v>10032</v>
       </c>
@@ -2273,16 +2334,16 @@
         <v>1003</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I13" s="1">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J13" s="1">
         <v>4</v>
@@ -2291,13 +2352,13 @@
         <v>5</v>
       </c>
       <c r="L13" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M13" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N13" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O13" s="1">
         <v>0</v>
@@ -2314,15 +2375,15 @@
       <c r="S13" s="1">
         <v>0</v>
       </c>
-      <c r="T13" s="4">
+      <c r="T13" s="1">
+        <v>0</v>
+      </c>
+      <c r="U13" s="1">
+        <v>0</v>
+      </c>
+      <c r="V13" s="4">
         <v>10</v>
       </c>
-      <c r="X13" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="1">
-        <v>0</v>
-      </c>
       <c r="Z13" s="1">
         <v>0</v>
       </c>
@@ -2332,8 +2393,14 @@
       <c r="AB13" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:35">
+      <c r="AC13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:37">
       <c r="C14" s="1">
         <v>10042</v>
       </c>
@@ -2344,16 +2411,16 @@
         <v>1004</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I14" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J14" s="1">
         <v>4</v>
@@ -2362,13 +2429,13 @@
         <v>5</v>
       </c>
       <c r="L14" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M14" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N14" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O14" s="1">
         <v>0</v>
@@ -2385,15 +2452,15 @@
       <c r="S14" s="1">
         <v>0</v>
       </c>
-      <c r="T14" s="4">
+      <c r="T14" s="1">
+        <v>0</v>
+      </c>
+      <c r="U14" s="1">
+        <v>0</v>
+      </c>
+      <c r="V14" s="4">
         <v>30</v>
       </c>
-      <c r="U14" s="1">
-        <v>0</v>
-      </c>
-      <c r="V14" s="1">
-        <v>0</v>
-      </c>
       <c r="W14" s="1">
         <v>0</v>
       </c>
@@ -2412,8 +2479,14 @@
       <c r="AB14" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:35">
+      <c r="AC14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:37">
       <c r="C15" s="1">
         <v>10052</v>
       </c>
@@ -2424,16 +2497,16 @@
         <v>1005</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I15" s="1">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J15" s="1">
         <v>4</v>
@@ -2442,13 +2515,13 @@
         <v>5</v>
       </c>
       <c r="L15" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="M15" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N15" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O15" s="1">
         <v>0</v>
@@ -2462,17 +2535,17 @@
       <c r="R15" s="1">
         <v>0</v>
       </c>
-      <c r="S15" s="4">
+      <c r="S15" s="1">
         <v>0</v>
       </c>
       <c r="T15" s="1">
-        <v>5</v>
-      </c>
-      <c r="U15" s="1">
+        <v>0</v>
+      </c>
+      <c r="U15" s="4">
         <v>0</v>
       </c>
       <c r="V15" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W15" s="1">
         <v>0</v>
@@ -2492,8 +2565,14 @@
       <c r="AB15" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:35">
+      <c r="AC15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:37">
       <c r="C16" s="1">
         <v>10062</v>
       </c>
@@ -2504,16 +2583,16 @@
         <v>1006</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I16" s="1">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="J16" s="1">
         <v>4</v>
@@ -2522,13 +2601,13 @@
         <v>5</v>
       </c>
       <c r="L16" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="M16" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N16" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O16" s="1">
         <v>0</v>
@@ -2542,18 +2621,18 @@
       <c r="R16" s="1">
         <v>0</v>
       </c>
-      <c r="S16" s="4">
+      <c r="S16" s="1">
         <v>0</v>
       </c>
       <c r="T16" s="1">
+        <v>0</v>
+      </c>
+      <c r="U16" s="4">
+        <v>0</v>
+      </c>
+      <c r="V16" s="1">
         <v>1</v>
       </c>
-      <c r="U16" s="1">
-        <v>0</v>
-      </c>
-      <c r="V16" s="1">
-        <v>0</v>
-      </c>
       <c r="W16" s="1">
         <v>0</v>
       </c>
@@ -2572,8 +2651,14 @@
       <c r="AB16" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:35">
+      <c r="AC16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:38">
       <c r="C17" s="1">
         <v>10072</v>
       </c>
@@ -2584,22 +2669,31 @@
         <v>1007</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
+      </c>
+      <c r="I17" s="1">
+        <v>10</v>
+      </c>
+      <c r="J17" s="1">
+        <v>4</v>
+      </c>
+      <c r="K17" s="1">
+        <v>5</v>
       </c>
       <c r="L17" s="1">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="M17" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N17" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O17" s="1">
         <v>0</v>
@@ -2616,15 +2710,15 @@
       <c r="S17" s="1">
         <v>0</v>
       </c>
-      <c r="T17" s="4">
+      <c r="T17" s="1">
+        <v>0</v>
+      </c>
+      <c r="U17" s="1">
+        <v>0</v>
+      </c>
+      <c r="V17" s="4">
         <v>50</v>
       </c>
-      <c r="U17" s="1">
-        <v>0</v>
-      </c>
-      <c r="V17" s="1">
-        <v>0</v>
-      </c>
       <c r="W17" s="1">
         <v>0</v>
       </c>
@@ -2643,12 +2737,18 @@
       <c r="AB17" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:35">
+      <c r="AC17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:38">
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
     </row>
-    <row r="19" customHeight="1" spans="3:35">
+    <row r="19" customHeight="1" spans="3:38">
       <c r="C19" s="1">
         <v>10023</v>
       </c>
@@ -2659,13 +2759,13 @@
         <v>1002</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I19" s="1">
         <v>20</v>
@@ -2677,13 +2777,13 @@
         <v>5</v>
       </c>
       <c r="L19" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M19" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N19" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O19" s="1">
         <v>0</v>
@@ -2713,22 +2813,28 @@
         <v>0</v>
       </c>
       <c r="X19" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="1">
         <v>10</v>
       </c>
-      <c r="Y19" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="1">
-        <v>0</v>
-      </c>
       <c r="AA19" s="1">
         <v>0</v>
       </c>
       <c r="AB19" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:35">
+      <c r="AC19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:38">
       <c r="C20" s="1">
         <v>10033</v>
       </c>
@@ -2739,16 +2845,16 @@
         <v>1003</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I20" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J20" s="1">
         <v>5</v>
@@ -2757,13 +2863,13 @@
         <v>5</v>
       </c>
       <c r="L20" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M20" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N20" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O20" s="1">
         <v>0</v>
@@ -2793,22 +2899,28 @@
         <v>0</v>
       </c>
       <c r="X20" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="1">
         <v>10</v>
       </c>
-      <c r="Y20" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="1">
-        <v>0</v>
-      </c>
       <c r="AA20" s="1">
         <v>0</v>
       </c>
       <c r="AB20" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:35">
+      <c r="AC20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:38">
       <c r="C21" s="1">
         <v>10043</v>
       </c>
@@ -2819,31 +2931,31 @@
         <v>1004</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I21" s="1">
+        <v>10</v>
+      </c>
+      <c r="J21" s="1">
+        <v>5</v>
+      </c>
+      <c r="K21" s="1">
+        <v>5</v>
+      </c>
+      <c r="L21" s="1">
         <v>20</v>
       </c>
-      <c r="J21" s="1">
-        <v>5</v>
-      </c>
-      <c r="K21" s="1">
-        <v>5</v>
-      </c>
-      <c r="L21" s="1">
-        <v>4</v>
-      </c>
       <c r="M21" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N21" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O21" s="1">
         <v>0</v>
@@ -2873,22 +2985,28 @@
         <v>0</v>
       </c>
       <c r="X21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="1">
         <v>10</v>
       </c>
-      <c r="Y21" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="1">
-        <v>0</v>
-      </c>
       <c r="AA21" s="1">
         <v>0</v>
       </c>
       <c r="AB21" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:35">
+      <c r="AC21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:38">
       <c r="C22" s="1">
         <v>10073</v>
       </c>
@@ -2899,16 +3017,16 @@
         <v>1007</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I22" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J22" s="1">
         <v>5</v>
@@ -2917,13 +3035,13 @@
         <v>5</v>
       </c>
       <c r="L22" s="1">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="M22" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N22" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O22" s="1">
         <v>0</v>
@@ -2953,34 +3071,41 @@
         <v>0</v>
       </c>
       <c r="X22" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="1">
         <v>10</v>
       </c>
-      <c r="Y22" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="1">
-        <v>0</v>
-      </c>
       <c r="AA22" s="1">
         <v>0</v>
       </c>
       <c r="AB22" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:35">
-      <c r="AA23" s="4"/>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:35">
-      <c r="AC24" s="1"/>
-      <c r="AD24" s="1"/>
+      <c r="AC22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:38">
+      <c r="AC23" s="4"/>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:38">
       <c r="AE24" s="1"/>
       <c r="AF24" s="1"/>
       <c r="AG24" s="1"/>
       <c r="AH24" s="1"/>
       <c r="AI24" s="1"/>
-    </row>
-    <row r="26" customHeight="1" spans="3:35">
+      <c r="AJ24" s="1"/>
+      <c r="AK24" s="1"/>
+      <c r="AL24" s="1"/>
+    </row>
+    <row r="26" customHeight="1" spans="3:38">
       <c r="C26" s="1">
         <v>20011</v>
       </c>
@@ -2991,13 +3116,13 @@
         <v>2001</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I26" s="1">
         <v>100</v>
@@ -3009,13 +3134,13 @@
         <v>5</v>
       </c>
       <c r="L26" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M26" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N26" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O26" s="1">
         <v>0</v>
@@ -3029,15 +3154,15 @@
       <c r="R26" s="1">
         <v>0</v>
       </c>
-      <c r="S26" s="4">
+      <c r="S26" s="1">
+        <v>0</v>
+      </c>
+      <c r="T26" s="1">
+        <v>0</v>
+      </c>
+      <c r="U26" s="4">
         <v>100</v>
       </c>
-      <c r="T26" s="1">
-        <v>0</v>
-      </c>
-      <c r="U26" s="1">
-        <v>0</v>
-      </c>
       <c r="V26" s="1">
         <v>0</v>
       </c>
@@ -3059,8 +3184,14 @@
       <c r="AB26" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:35">
+      <c r="AC26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:38">
       <c r="C27" s="1">
         <v>20021</v>
       </c>
@@ -3071,16 +3202,16 @@
         <v>2002</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I27" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J27" s="1">
         <v>1</v>
@@ -3089,13 +3220,13 @@
         <v>5</v>
       </c>
       <c r="L27" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M27" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N27" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O27" s="1">
         <v>0</v>
@@ -3109,15 +3240,15 @@
       <c r="R27" s="1">
         <v>0</v>
       </c>
-      <c r="S27" s="4">
+      <c r="S27" s="1">
+        <v>0</v>
+      </c>
+      <c r="T27" s="1">
+        <v>0</v>
+      </c>
+      <c r="U27" s="4">
         <v>1000</v>
       </c>
-      <c r="T27" s="1">
-        <v>0</v>
-      </c>
-      <c r="U27" s="1">
-        <v>0</v>
-      </c>
       <c r="V27" s="1">
         <v>0</v>
       </c>
@@ -3139,8 +3270,14 @@
       <c r="AB27" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:35">
+      <c r="AC27" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:38">
       <c r="C28" s="1">
         <v>20031</v>
       </c>
@@ -3151,16 +3288,16 @@
         <v>2003</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I28" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J28" s="1">
         <v>1</v>
@@ -3169,13 +3306,13 @@
         <v>5</v>
       </c>
       <c r="L28" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M28" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N28" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O28" s="1">
         <v>0</v>
@@ -3189,15 +3326,15 @@
       <c r="R28" s="1">
         <v>0</v>
       </c>
-      <c r="S28" s="4">
+      <c r="S28" s="1">
+        <v>0</v>
+      </c>
+      <c r="T28" s="1">
+        <v>0</v>
+      </c>
+      <c r="U28" s="4">
         <v>800</v>
       </c>
-      <c r="T28" s="1">
-        <v>0</v>
-      </c>
-      <c r="U28" s="1">
-        <v>0</v>
-      </c>
       <c r="V28" s="1">
         <v>0</v>
       </c>
@@ -3219,8 +3356,14 @@
       <c r="AB28" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:35">
+      <c r="AC28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:38">
       <c r="C29" s="1">
         <v>20041</v>
       </c>
@@ -3231,16 +3374,16 @@
         <v>2004</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I29" s="1">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="J29" s="1">
         <v>1</v>
@@ -3249,13 +3392,13 @@
         <v>5</v>
       </c>
       <c r="L29" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M29" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N29" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O29" s="1">
         <v>0</v>
@@ -3269,15 +3412,15 @@
       <c r="R29" s="1">
         <v>0</v>
       </c>
-      <c r="S29" s="4">
+      <c r="S29" s="1">
+        <v>0</v>
+      </c>
+      <c r="T29" s="1">
+        <v>0</v>
+      </c>
+      <c r="U29" s="4">
         <v>2000</v>
       </c>
-      <c r="T29" s="1">
-        <v>0</v>
-      </c>
-      <c r="U29" s="1">
-        <v>0</v>
-      </c>
       <c r="V29" s="1">
         <v>0</v>
       </c>
@@ -3299,8 +3442,14 @@
       <c r="AB29" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:35">
+      <c r="AC29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:38">
       <c r="C30" s="1">
         <v>20071</v>
       </c>
@@ -3311,16 +3460,16 @@
         <v>2007</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I30" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="J30" s="1">
         <v>1</v>
@@ -3329,13 +3478,13 @@
         <v>5</v>
       </c>
       <c r="L30" s="1">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="M30" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N30" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O30" s="1">
         <v>0</v>
@@ -3349,15 +3498,15 @@
       <c r="R30" s="1">
         <v>0</v>
       </c>
-      <c r="S30" s="4">
+      <c r="S30" s="1">
+        <v>0</v>
+      </c>
+      <c r="T30" s="1">
+        <v>0</v>
+      </c>
+      <c r="U30" s="4">
         <v>10000</v>
       </c>
-      <c r="T30" s="1">
-        <v>0</v>
-      </c>
-      <c r="U30" s="1">
-        <v>0</v>
-      </c>
       <c r="V30" s="1">
         <v>0</v>
       </c>
@@ -3379,21 +3528,27 @@
       <c r="AB30" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:35">
+      <c r="AC30" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:38">
       <c r="F31" s="4"/>
-      <c r="U31" s="1">
-        <v>0</v>
-      </c>
-      <c r="V31" s="1">
-        <v>0</v>
-      </c>
       <c r="W31" s="1">
         <v>0</v>
       </c>
-      <c r="AA31" s="4"/>
-    </row>
-    <row r="32" customHeight="1" spans="3:35">
+      <c r="X31" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="4"/>
+    </row>
+    <row r="32" customHeight="1" spans="3:38">
       <c r="C32" s="1">
         <v>20022</v>
       </c>
@@ -3404,13 +3559,13 @@
         <v>2002</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I32" s="1">
         <v>60</v>
@@ -3422,13 +3577,13 @@
         <v>5</v>
       </c>
       <c r="L32" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M32" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N32" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O32" s="1">
         <v>0</v>
@@ -3445,15 +3600,15 @@
       <c r="S32" s="1">
         <v>0</v>
       </c>
-      <c r="T32" s="4">
+      <c r="T32" s="1">
+        <v>0</v>
+      </c>
+      <c r="U32" s="1">
+        <v>0</v>
+      </c>
+      <c r="V32" s="4">
         <v>20</v>
       </c>
-      <c r="U32" s="1">
-        <v>0</v>
-      </c>
-      <c r="V32" s="1">
-        <v>0</v>
-      </c>
       <c r="W32" s="1">
         <v>0</v>
       </c>
@@ -3472,8 +3627,14 @@
       <c r="AB32" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:35">
+      <c r="AC32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:38">
       <c r="C33" s="1">
         <v>20032</v>
       </c>
@@ -3484,16 +3645,16 @@
         <v>2003</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I33" s="1">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J33" s="1">
         <v>4</v>
@@ -3502,13 +3663,13 @@
         <v>5</v>
       </c>
       <c r="L33" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M33" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N33" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O33" s="1">
         <v>0</v>
@@ -3525,15 +3686,15 @@
       <c r="S33" s="1">
         <v>0</v>
       </c>
-      <c r="T33" s="4">
+      <c r="T33" s="1">
+        <v>0</v>
+      </c>
+      <c r="U33" s="1">
+        <v>0</v>
+      </c>
+      <c r="V33" s="4">
         <v>10</v>
       </c>
-      <c r="U33" s="1">
-        <v>0</v>
-      </c>
-      <c r="V33" s="1">
-        <v>0</v>
-      </c>
       <c r="W33" s="1">
         <v>0</v>
       </c>
@@ -3552,8 +3713,14 @@
       <c r="AB33" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:35">
+      <c r="AC33" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:38">
       <c r="C34" s="1">
         <v>20042</v>
       </c>
@@ -3564,16 +3731,16 @@
         <v>2004</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I34" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J34" s="1">
         <v>4</v>
@@ -3582,13 +3749,13 @@
         <v>5</v>
       </c>
       <c r="L34" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M34" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N34" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O34" s="1">
         <v>0</v>
@@ -3605,15 +3772,15 @@
       <c r="S34" s="1">
         <v>0</v>
       </c>
-      <c r="T34" s="4">
+      <c r="T34" s="1">
+        <v>0</v>
+      </c>
+      <c r="U34" s="1">
+        <v>0</v>
+      </c>
+      <c r="V34" s="4">
         <v>30</v>
       </c>
-      <c r="U34" s="1">
-        <v>0</v>
-      </c>
-      <c r="V34" s="1">
-        <v>0</v>
-      </c>
       <c r="W34" s="1">
         <v>0</v>
       </c>
@@ -3632,8 +3799,14 @@
       <c r="AB34" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:35">
+      <c r="AC34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:38">
       <c r="C35" s="1">
         <v>20052</v>
       </c>
@@ -3644,16 +3817,16 @@
         <v>2005</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I35" s="1">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J35" s="1">
         <v>4</v>
@@ -3662,13 +3835,13 @@
         <v>5</v>
       </c>
       <c r="L35" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="M35" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N35" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O35" s="1">
         <v>0</v>
@@ -3682,17 +3855,17 @@
       <c r="R35" s="1">
         <v>0</v>
       </c>
-      <c r="S35" s="4">
+      <c r="S35" s="1">
+        <v>0</v>
+      </c>
+      <c r="T35" s="1">
+        <v>0</v>
+      </c>
+      <c r="U35" s="4">
         <v>50</v>
       </c>
-      <c r="T35" s="1">
-        <v>5</v>
-      </c>
-      <c r="U35" s="1">
-        <v>0</v>
-      </c>
       <c r="V35" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W35" s="1">
         <v>0</v>
@@ -3712,8 +3885,14 @@
       <c r="AB35" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:35">
+      <c r="AC35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:38">
       <c r="C36" s="1">
         <v>20062</v>
       </c>
@@ -3724,16 +3903,16 @@
         <v>2006</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I36" s="1">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="J36" s="1">
         <v>4</v>
@@ -3742,13 +3921,13 @@
         <v>5</v>
       </c>
       <c r="L36" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="M36" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N36" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O36" s="1">
         <v>0</v>
@@ -3762,18 +3941,18 @@
       <c r="R36" s="1">
         <v>0</v>
       </c>
-      <c r="S36" s="4">
+      <c r="S36" s="1">
         <v>0</v>
       </c>
       <c r="T36" s="1">
+        <v>0</v>
+      </c>
+      <c r="U36" s="4">
+        <v>0</v>
+      </c>
+      <c r="V36" s="1">
         <v>1</v>
       </c>
-      <c r="U36" s="1">
-        <v>0</v>
-      </c>
-      <c r="V36" s="1">
-        <v>0</v>
-      </c>
       <c r="W36" s="1">
         <v>0</v>
       </c>
@@ -3792,8 +3971,14 @@
       <c r="AB36" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:35">
+      <c r="AC36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:38">
       <c r="C37" s="1">
         <v>20072</v>
       </c>
@@ -3804,22 +3989,31 @@
         <v>2007</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
+      </c>
+      <c r="I37" s="1">
+        <v>10</v>
+      </c>
+      <c r="J37" s="1">
+        <v>4</v>
+      </c>
+      <c r="K37" s="1">
+        <v>5</v>
       </c>
       <c r="L37" s="1">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="M37" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N37" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O37" s="1">
         <v>0</v>
@@ -3836,15 +4030,15 @@
       <c r="S37" s="1">
         <v>0</v>
       </c>
-      <c r="T37" s="4">
+      <c r="T37" s="1">
+        <v>0</v>
+      </c>
+      <c r="U37" s="1">
+        <v>0</v>
+      </c>
+      <c r="V37" s="4">
         <v>50</v>
       </c>
-      <c r="U37" s="1">
-        <v>0</v>
-      </c>
-      <c r="V37" s="1">
-        <v>0</v>
-      </c>
       <c r="W37" s="1">
         <v>0</v>
       </c>
@@ -3863,21 +4057,27 @@
       <c r="AB37" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:35">
+      <c r="AC37" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:38">
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
-      <c r="U38" s="1">
-        <v>0</v>
-      </c>
-      <c r="V38" s="1">
-        <v>0</v>
-      </c>
       <c r="W38" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:35">
+      <c r="X38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:38">
       <c r="C39" s="1">
         <v>20023</v>
       </c>
@@ -3888,13 +4088,13 @@
         <v>2002</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I39" s="1">
         <v>20</v>
@@ -3906,13 +4106,13 @@
         <v>5</v>
       </c>
       <c r="L39" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M39" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N39" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O39" s="1">
         <v>0</v>
@@ -3942,22 +4142,28 @@
         <v>0</v>
       </c>
       <c r="X39" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="1">
         <v>10</v>
       </c>
-      <c r="Y39" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z39" s="1">
-        <v>0</v>
-      </c>
       <c r="AA39" s="1">
         <v>0</v>
       </c>
       <c r="AB39" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:35">
+      <c r="AC39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:38">
       <c r="C40" s="1">
         <v>20033</v>
       </c>
@@ -3968,16 +4174,16 @@
         <v>2003</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I40" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J40" s="1">
         <v>5</v>
@@ -3986,13 +4192,13 @@
         <v>5</v>
       </c>
       <c r="L40" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M40" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N40" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O40" s="1">
         <v>0</v>
@@ -4022,22 +4228,28 @@
         <v>0</v>
       </c>
       <c r="X40" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="1">
         <v>10</v>
       </c>
-      <c r="Y40" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z40" s="1">
-        <v>0</v>
-      </c>
       <c r="AA40" s="1">
         <v>0</v>
       </c>
       <c r="AB40" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:35">
+      <c r="AC40" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:38">
       <c r="C41" s="1">
         <v>20043</v>
       </c>
@@ -4048,31 +4260,31 @@
         <v>2004</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I41" s="1">
+        <v>10</v>
+      </c>
+      <c r="J41" s="1">
+        <v>5</v>
+      </c>
+      <c r="K41" s="1">
+        <v>5</v>
+      </c>
+      <c r="L41" s="1">
         <v>20</v>
       </c>
-      <c r="J41" s="1">
-        <v>5</v>
-      </c>
-      <c r="K41" s="1">
-        <v>5</v>
-      </c>
-      <c r="L41" s="1">
-        <v>4</v>
-      </c>
       <c r="M41" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N41" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O41" s="1">
         <v>0</v>
@@ -4102,22 +4314,28 @@
         <v>0</v>
       </c>
       <c r="X41" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="1">
         <v>10</v>
       </c>
-      <c r="Y41" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z41" s="1">
-        <v>0</v>
-      </c>
       <c r="AA41" s="1">
         <v>0</v>
       </c>
       <c r="AB41" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:35">
+      <c r="AC41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:38">
       <c r="C42" s="1">
         <v>20073</v>
       </c>
@@ -4128,16 +4346,16 @@
         <v>2007</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I42" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J42" s="1">
         <v>5</v>
@@ -4146,13 +4364,13 @@
         <v>5</v>
       </c>
       <c r="L42" s="1">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="M42" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N42" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O42" s="1">
         <v>0</v>
@@ -4182,31 +4400,38 @@
         <v>0</v>
       </c>
       <c r="X42" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="1">
         <v>10</v>
       </c>
-      <c r="Y42" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="1">
-        <v>0</v>
-      </c>
       <c r="AA42" s="1">
         <v>0</v>
       </c>
       <c r="AB42" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:35">
-      <c r="AC44" s="1"/>
-      <c r="AD44" s="1"/>
+      <c r="AC42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:38">
       <c r="AE44" s="1"/>
       <c r="AF44" s="1"/>
       <c r="AG44" s="1"/>
       <c r="AH44" s="1"/>
       <c r="AI44" s="1"/>
-    </row>
-    <row r="46" customHeight="1" spans="3:35">
+      <c r="AJ44" s="1"/>
+      <c r="AK44" s="1"/>
+      <c r="AL44" s="1"/>
+    </row>
+    <row r="46" customHeight="1" spans="3:38">
       <c r="C46" s="1">
         <v>30011</v>
       </c>
@@ -4217,13 +4442,13 @@
         <v>3001</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I46" s="1">
         <v>100</v>
@@ -4235,13 +4460,13 @@
         <v>5</v>
       </c>
       <c r="L46" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M46" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N46" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O46" s="1">
         <v>0</v>
@@ -4255,15 +4480,15 @@
       <c r="R46" s="1">
         <v>0</v>
       </c>
-      <c r="S46" s="4">
+      <c r="S46" s="1">
+        <v>0</v>
+      </c>
+      <c r="T46" s="1">
+        <v>0</v>
+      </c>
+      <c r="U46" s="4">
         <v>100</v>
       </c>
-      <c r="T46" s="1">
-        <v>0</v>
-      </c>
-      <c r="U46" s="1">
-        <v>0</v>
-      </c>
       <c r="V46" s="1">
         <v>0</v>
       </c>
@@ -4285,8 +4510,14 @@
       <c r="AB46" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:35">
+      <c r="AC46" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:38">
       <c r="C47" s="1">
         <v>30021</v>
       </c>
@@ -4297,16 +4528,16 @@
         <v>3002</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I47" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J47" s="1">
         <v>1</v>
@@ -4315,13 +4546,13 @@
         <v>5</v>
       </c>
       <c r="L47" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M47" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N47" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O47" s="1">
         <v>0</v>
@@ -4335,15 +4566,15 @@
       <c r="R47" s="1">
         <v>0</v>
       </c>
-      <c r="S47" s="4">
+      <c r="S47" s="1">
+        <v>0</v>
+      </c>
+      <c r="T47" s="1">
+        <v>0</v>
+      </c>
+      <c r="U47" s="4">
         <v>1000</v>
       </c>
-      <c r="T47" s="1">
-        <v>0</v>
-      </c>
-      <c r="U47" s="1">
-        <v>0</v>
-      </c>
       <c r="V47" s="1">
         <v>0</v>
       </c>
@@ -4365,8 +4596,14 @@
       <c r="AB47" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:35">
+      <c r="AC47" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:38">
       <c r="C48" s="1">
         <v>30031</v>
       </c>
@@ -4377,16 +4614,16 @@
         <v>3003</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I48" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J48" s="1">
         <v>1</v>
@@ -4395,13 +4632,13 @@
         <v>5</v>
       </c>
       <c r="L48" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M48" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N48" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O48" s="1">
         <v>0</v>
@@ -4415,15 +4652,15 @@
       <c r="R48" s="1">
         <v>0</v>
       </c>
-      <c r="S48" s="4">
+      <c r="S48" s="1">
+        <v>0</v>
+      </c>
+      <c r="T48" s="1">
+        <v>0</v>
+      </c>
+      <c r="U48" s="4">
         <v>800</v>
       </c>
-      <c r="T48" s="1">
-        <v>0</v>
-      </c>
-      <c r="U48" s="1">
-        <v>0</v>
-      </c>
       <c r="V48" s="1">
         <v>0</v>
       </c>
@@ -4445,8 +4682,14 @@
       <c r="AB48" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:28">
+      <c r="AC48" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:30">
       <c r="C49" s="1">
         <v>30041</v>
       </c>
@@ -4457,16 +4700,16 @@
         <v>3004</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I49" s="1">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="J49" s="1">
         <v>1</v>
@@ -4475,13 +4718,13 @@
         <v>5</v>
       </c>
       <c r="L49" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M49" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N49" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O49" s="1">
         <v>0</v>
@@ -4495,15 +4738,15 @@
       <c r="R49" s="1">
         <v>0</v>
       </c>
-      <c r="S49" s="4">
+      <c r="S49" s="1">
+        <v>0</v>
+      </c>
+      <c r="T49" s="1">
+        <v>0</v>
+      </c>
+      <c r="U49" s="4">
         <v>30000</v>
       </c>
-      <c r="T49" s="1">
-        <v>0</v>
-      </c>
-      <c r="U49" s="1">
-        <v>0</v>
-      </c>
       <c r="V49" s="1">
         <v>0</v>
       </c>
@@ -4525,8 +4768,14 @@
       <c r="AB49" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:28">
+      <c r="AC49" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:30">
       <c r="C50" s="1">
         <v>30071</v>
       </c>
@@ -4537,16 +4786,16 @@
         <v>3007</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I50" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="J50" s="1">
         <v>1</v>
@@ -4555,13 +4804,13 @@
         <v>5</v>
       </c>
       <c r="L50" s="1">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="M50" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N50" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O50" s="1">
         <v>0</v>
@@ -4575,15 +4824,15 @@
       <c r="R50" s="1">
         <v>0</v>
       </c>
-      <c r="S50" s="4">
+      <c r="S50" s="1">
+        <v>0</v>
+      </c>
+      <c r="T50" s="1">
+        <v>0</v>
+      </c>
+      <c r="U50" s="4">
         <v>10000</v>
       </c>
-      <c r="T50" s="1">
-        <v>0</v>
-      </c>
-      <c r="U50" s="1">
-        <v>0</v>
-      </c>
       <c r="V50" s="1">
         <v>0</v>
       </c>
@@ -4605,12 +4854,18 @@
       <c r="AB50" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:28">
+      <c r="AC50" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:30">
       <c r="F51" s="4"/>
-      <c r="AA51" s="4"/>
-    </row>
-    <row r="52" customHeight="1" spans="3:28">
+      <c r="AC51" s="4"/>
+    </row>
+    <row r="52" customHeight="1" spans="3:30">
       <c r="C52" s="1">
         <v>30022</v>
       </c>
@@ -4621,13 +4876,13 @@
         <v>3002</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I52" s="1">
         <v>60</v>
@@ -4639,13 +4894,13 @@
         <v>5</v>
       </c>
       <c r="L52" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M52" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N52" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O52" s="1">
         <v>0</v>
@@ -4662,15 +4917,15 @@
       <c r="S52" s="1">
         <v>0</v>
       </c>
-      <c r="T52" s="4">
+      <c r="T52" s="1">
+        <v>0</v>
+      </c>
+      <c r="U52" s="1">
+        <v>0</v>
+      </c>
+      <c r="V52" s="4">
         <v>20</v>
       </c>
-      <c r="U52" s="1">
-        <v>0</v>
-      </c>
-      <c r="V52" s="1">
-        <v>0</v>
-      </c>
       <c r="W52" s="1">
         <v>0</v>
       </c>
@@ -4689,8 +4944,14 @@
       <c r="AB52" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:28">
+      <c r="AC52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:30">
       <c r="C53" s="1">
         <v>30032</v>
       </c>
@@ -4701,16 +4962,16 @@
         <v>3003</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I53" s="1">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J53" s="1">
         <v>4</v>
@@ -4719,13 +4980,13 @@
         <v>5</v>
       </c>
       <c r="L53" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M53" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N53" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O53" s="1">
         <v>0</v>
@@ -4742,15 +5003,15 @@
       <c r="S53" s="1">
         <v>0</v>
       </c>
-      <c r="T53" s="4">
+      <c r="T53" s="1">
+        <v>0</v>
+      </c>
+      <c r="U53" s="1">
+        <v>0</v>
+      </c>
+      <c r="V53" s="4">
         <v>10</v>
       </c>
-      <c r="U53" s="1">
-        <v>0</v>
-      </c>
-      <c r="V53" s="1">
-        <v>0</v>
-      </c>
       <c r="W53" s="1">
         <v>0</v>
       </c>
@@ -4769,8 +5030,14 @@
       <c r="AB53" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:28">
+      <c r="AC53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:30">
       <c r="C54" s="1">
         <v>30042</v>
       </c>
@@ -4781,16 +5048,16 @@
         <v>3004</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I54" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J54" s="1">
         <v>4</v>
@@ -4799,13 +5066,13 @@
         <v>5</v>
       </c>
       <c r="L54" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M54" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N54" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O54" s="1">
         <v>0</v>
@@ -4822,15 +5089,15 @@
       <c r="S54" s="1">
         <v>0</v>
       </c>
-      <c r="T54" s="4">
+      <c r="T54" s="1">
+        <v>0</v>
+      </c>
+      <c r="U54" s="1">
+        <v>0</v>
+      </c>
+      <c r="V54" s="4">
         <v>100</v>
       </c>
-      <c r="U54" s="1">
-        <v>0</v>
-      </c>
-      <c r="V54" s="1">
-        <v>0</v>
-      </c>
       <c r="W54" s="1">
         <v>0</v>
       </c>
@@ -4849,8 +5116,14 @@
       <c r="AB54" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:28">
+      <c r="AC54" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:30">
       <c r="C55" s="1">
         <v>30052</v>
       </c>
@@ -4861,16 +5134,16 @@
         <v>3005</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I55" s="1">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J55" s="1">
         <v>4</v>
@@ -4879,13 +5152,13 @@
         <v>5</v>
       </c>
       <c r="L55" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="M55" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N55" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O55" s="1">
         <v>0</v>
@@ -4899,17 +5172,17 @@
       <c r="R55" s="1">
         <v>0</v>
       </c>
-      <c r="S55" s="4">
+      <c r="S55" s="1">
+        <v>0</v>
+      </c>
+      <c r="T55" s="1">
+        <v>0</v>
+      </c>
+      <c r="U55" s="4">
         <v>50</v>
       </c>
-      <c r="T55" s="1">
-        <v>5</v>
-      </c>
-      <c r="U55" s="1">
-        <v>0</v>
-      </c>
       <c r="V55" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W55" s="1">
         <v>0</v>
@@ -4929,8 +5202,14 @@
       <c r="AB55" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:28">
+      <c r="AC55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:30">
       <c r="C56" s="1">
         <v>30062</v>
       </c>
@@ -4941,16 +5220,16 @@
         <v>3006</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I56" s="1">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="J56" s="1">
         <v>4</v>
@@ -4959,13 +5238,13 @@
         <v>5</v>
       </c>
       <c r="L56" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="M56" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N56" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O56" s="1">
         <v>0</v>
@@ -4979,18 +5258,18 @@
       <c r="R56" s="1">
         <v>0</v>
       </c>
-      <c r="S56" s="4">
+      <c r="S56" s="1">
         <v>0</v>
       </c>
       <c r="T56" s="1">
+        <v>0</v>
+      </c>
+      <c r="U56" s="4">
+        <v>0</v>
+      </c>
+      <c r="V56" s="1">
         <v>1</v>
       </c>
-      <c r="U56" s="1">
-        <v>0</v>
-      </c>
-      <c r="V56" s="1">
-        <v>0</v>
-      </c>
       <c r="W56" s="1">
         <v>0</v>
       </c>
@@ -5009,8 +5288,14 @@
       <c r="AB56" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:28">
+      <c r="AC56" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD56" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:30">
       <c r="C57" s="1">
         <v>30072</v>
       </c>
@@ -5021,16 +5306,16 @@
         <v>3007</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I57" s="1">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="J57" s="1">
         <v>4</v>
@@ -5039,13 +5324,13 @@
         <v>5</v>
       </c>
       <c r="L57" s="1">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="M57" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N57" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O57" s="1">
         <v>0</v>
@@ -5062,15 +5347,15 @@
       <c r="S57" s="1">
         <v>0</v>
       </c>
-      <c r="T57" s="4">
+      <c r="T57" s="1">
+        <v>0</v>
+      </c>
+      <c r="U57" s="1">
+        <v>0</v>
+      </c>
+      <c r="V57" s="4">
         <v>50</v>
       </c>
-      <c r="U57" s="1">
-        <v>0</v>
-      </c>
-      <c r="V57" s="1">
-        <v>0</v>
-      </c>
       <c r="W57" s="1">
         <v>0</v>
       </c>
@@ -5089,12 +5374,18 @@
       <c r="AB57" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:28">
+      <c r="AC57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:30">
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
     </row>
-    <row r="59" customHeight="1" spans="3:28">
+    <row r="59" customHeight="1" spans="3:30">
       <c r="C59" s="1">
         <v>30023</v>
       </c>
@@ -5105,13 +5396,13 @@
         <v>3002</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I59" s="1">
         <v>20</v>
@@ -5123,13 +5414,13 @@
         <v>5</v>
       </c>
       <c r="L59" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M59" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N59" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O59" s="1">
         <v>0</v>
@@ -5159,22 +5450,28 @@
         <v>0</v>
       </c>
       <c r="X59" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="1">
         <v>10</v>
       </c>
-      <c r="Y59" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z59" s="1">
-        <v>0</v>
-      </c>
       <c r="AA59" s="1">
         <v>0</v>
       </c>
       <c r="AB59" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" customHeight="1" spans="3:28">
+      <c r="AC59" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:30">
       <c r="C60" s="1">
         <v>30033</v>
       </c>
@@ -5185,16 +5482,16 @@
         <v>3003</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I60" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J60" s="1">
         <v>5</v>
@@ -5203,13 +5500,13 @@
         <v>5</v>
       </c>
       <c r="L60" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M60" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N60" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O60" s="1">
         <v>0</v>
@@ -5239,22 +5536,28 @@
         <v>0</v>
       </c>
       <c r="X60" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="1">
         <v>10</v>
       </c>
-      <c r="Y60" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z60" s="1">
-        <v>0</v>
-      </c>
       <c r="AA60" s="1">
         <v>0</v>
       </c>
       <c r="AB60" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:28">
+      <c r="AC60" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:30">
       <c r="C61" s="1">
         <v>30073</v>
       </c>
@@ -5265,16 +5568,16 @@
         <v>3007</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I61" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J61" s="1">
         <v>5</v>
@@ -5283,13 +5586,13 @@
         <v>5</v>
       </c>
       <c r="L61" s="1">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="M61" s="1">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N61" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O61" s="1">
         <v>0</v>
@@ -5319,24 +5622,30 @@
         <v>0</v>
       </c>
       <c r="X61" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="1">
         <v>10</v>
       </c>
-      <c r="Y61" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="1">
-        <v>0</v>
-      </c>
       <c r="AA61" s="1">
         <v>0</v>
       </c>
       <c r="AB61" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="1">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:M5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:M3 L4 M4 L5:M5 C3:K5 N3:O5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -643,12 +643,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="W12" s="1">
         <v>0</v>
@@ -2382,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Z13" s="1">
         <v>0</v>
@@ -3607,7 +3607,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="W32" s="1">
         <v>0</v>
@@ -3693,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W33" s="1">
         <v>0</v>
@@ -4924,7 +4924,7 @@
         <v>0</v>
       </c>
       <c r="V52" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="W52" s="1">
         <v>0</v>
@@ -5645,7 +5645,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:M3 L4 M4 L5:M5 C3:K5 N3:O5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:O5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -174,7 +174,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="100">
   <si>
     <t>#</t>
   </si>
@@ -389,6 +389,9 @@
     <t>·精进</t>
   </si>
   <si>
+    <t>增加{1}%物攻加成</t>
+  </si>
+  <si>
     <t>增加{1}%技能系数</t>
   </si>
   <si>
@@ -428,6 +431,9 @@
     <t>冰封术</t>
   </si>
   <si>
+    <t>增加{1}%魔法加成</t>
+  </si>
+  <si>
     <t>炎凰法盾</t>
   </si>
   <si>
@@ -456,6 +462,9 @@
   </si>
   <si>
     <t>增加{0}点神兽攻击</t>
+  </si>
+  <si>
+    <t>增加{1}%道术加成</t>
   </si>
   <si>
     <t>太虚麟盾</t>
@@ -643,12 +652,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1441,7 +1450,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AL61"/>
+  <dimension ref="C1:AL64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
@@ -2239,16 +2248,16 @@
     </row>
     <row r="12" customHeight="1" spans="3:37">
       <c r="C12" s="1">
-        <v>10022</v>
+        <v>10012</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
       </c>
       <c r="E12" s="4">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>70</v>
@@ -2257,7 +2266,7 @@
         <v>71</v>
       </c>
       <c r="I12" s="1">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J12" s="1">
         <v>4</v>
@@ -2296,7 +2305,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W12" s="1">
         <v>0</v>
@@ -2325,25 +2334,25 @@
     </row>
     <row r="13" customHeight="1" spans="3:37">
       <c r="C13" s="1">
-        <v>10032</v>
+        <v>10022</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
       </c>
       <c r="E13" s="4">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>70</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I13" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J13" s="1">
         <v>4</v>
@@ -2352,7 +2361,7 @@
         <v>5</v>
       </c>
       <c r="L13" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M13" s="1">
         <v>9999</v>
@@ -2382,7 +2391,16 @@
         <v>0</v>
       </c>
       <c r="V13" s="4">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="W13" s="1">
+        <v>0</v>
+      </c>
+      <c r="X13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>0</v>
       </c>
       <c r="Z13" s="1">
         <v>0</v>
@@ -2402,25 +2420,25 @@
     </row>
     <row r="14" customHeight="1" spans="3:37">
       <c r="C14" s="1">
-        <v>10042</v>
+        <v>10032</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
       </c>
       <c r="E14" s="4">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>70</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I14" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J14" s="1">
         <v>4</v>
@@ -2459,16 +2477,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="4">
-        <v>30</v>
-      </c>
-      <c r="W14" s="1">
-        <v>0</v>
-      </c>
-      <c r="X14" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z14" s="1">
         <v>0</v>
@@ -2488,25 +2497,25 @@
     </row>
     <row r="15" customHeight="1" spans="3:37">
       <c r="C15" s="1">
-        <v>10052</v>
+        <v>10042</v>
       </c>
       <c r="D15" s="1">
         <v>1</v>
       </c>
       <c r="E15" s="4">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F15" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="I15" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J15" s="1">
         <v>4</v>
@@ -2515,7 +2524,7 @@
         <v>5</v>
       </c>
       <c r="L15" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M15" s="1">
         <v>9999</v>
@@ -2541,11 +2550,11 @@
       <c r="T15" s="1">
         <v>0</v>
       </c>
-      <c r="U15" s="4">
-        <v>0</v>
-      </c>
-      <c r="V15" s="1">
-        <v>5</v>
+      <c r="U15" s="1">
+        <v>0</v>
+      </c>
+      <c r="V15" s="4">
+        <v>20</v>
       </c>
       <c r="W15" s="1">
         <v>0</v>
@@ -2574,25 +2583,25 @@
     </row>
     <row r="16" customHeight="1" spans="3:37">
       <c r="C16" s="1">
-        <v>10062</v>
+        <v>10052</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
       </c>
       <c r="E16" s="4">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="F16" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="I16" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J16" s="1">
         <v>4</v>
@@ -2631,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W16" s="1">
         <v>0</v>
@@ -2660,25 +2669,25 @@
     </row>
     <row r="17" customHeight="1" spans="3:38">
       <c r="C17" s="1">
-        <v>10072</v>
+        <v>10062</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
       </c>
       <c r="E17" s="4">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>70</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I17" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J17" s="1">
         <v>4</v>
@@ -2687,7 +2696,7 @@
         <v>5</v>
       </c>
       <c r="L17" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M17" s="1">
         <v>9999</v>
@@ -2713,148 +2722,148 @@
       <c r="T17" s="1">
         <v>0</v>
       </c>
-      <c r="U17" s="1">
-        <v>0</v>
-      </c>
-      <c r="V17" s="4">
+      <c r="U17" s="4">
+        <v>0</v>
+      </c>
+      <c r="V17" s="1">
+        <v>1</v>
+      </c>
+      <c r="W17" s="1">
+        <v>0</v>
+      </c>
+      <c r="X17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:38">
+      <c r="C18" s="1">
+        <v>10072</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4">
+        <v>1007</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" s="1">
+        <v>10</v>
+      </c>
+      <c r="J18" s="1">
+        <v>4</v>
+      </c>
+      <c r="K18" s="1">
+        <v>5</v>
+      </c>
+      <c r="L18" s="1">
+        <v>30</v>
+      </c>
+      <c r="M18" s="1">
+        <v>9999</v>
+      </c>
+      <c r="N18" s="1">
+        <v>4</v>
+      </c>
+      <c r="O18" s="1">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>0</v>
+      </c>
+      <c r="R18" s="1">
+        <v>0</v>
+      </c>
+      <c r="S18" s="1">
+        <v>0</v>
+      </c>
+      <c r="T18" s="1">
+        <v>0</v>
+      </c>
+      <c r="U18" s="1">
+        <v>0</v>
+      </c>
+      <c r="V18" s="4">
         <v>50</v>
       </c>
-      <c r="W17" s="1">
-        <v>0</v>
-      </c>
-      <c r="X17" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:38">
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
+      <c r="W18" s="1">
+        <v>0</v>
+      </c>
+      <c r="X18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="19" customHeight="1" spans="3:38">
-      <c r="C19" s="1">
-        <v>10023</v>
-      </c>
-      <c r="D19" s="1">
-        <v>1</v>
-      </c>
-      <c r="E19" s="4">
-        <v>1002</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I19" s="1">
-        <v>20</v>
-      </c>
-      <c r="J19" s="1">
-        <v>5</v>
-      </c>
-      <c r="K19" s="1">
-        <v>5</v>
-      </c>
-      <c r="L19" s="1">
-        <v>0</v>
-      </c>
-      <c r="M19" s="1">
-        <v>9999</v>
-      </c>
-      <c r="N19" s="1">
-        <v>4</v>
-      </c>
-      <c r="O19" s="1">
-        <v>0</v>
-      </c>
-      <c r="P19" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="1">
-        <v>0</v>
-      </c>
-      <c r="R19" s="1">
-        <v>0</v>
-      </c>
-      <c r="S19" s="1">
-        <v>0</v>
-      </c>
-      <c r="T19" s="1">
-        <v>0</v>
-      </c>
-      <c r="U19" s="1">
-        <v>0</v>
-      </c>
-      <c r="V19" s="1">
-        <v>0</v>
-      </c>
-      <c r="W19" s="1">
-        <v>0</v>
-      </c>
-      <c r="X19" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="1">
-        <v>10</v>
-      </c>
-      <c r="AA19" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD19" s="1">
-        <v>0</v>
-      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
     </row>
     <row r="20" customHeight="1" spans="3:38">
       <c r="C20" s="1">
-        <v>10033</v>
+        <v>10023</v>
       </c>
       <c r="D20" s="1">
         <v>1</v>
       </c>
       <c r="E20" s="4">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I20" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J20" s="1">
         <v>5</v>
@@ -2863,7 +2872,7 @@
         <v>5</v>
       </c>
       <c r="L20" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M20" s="1">
         <v>9999</v>
@@ -2922,34 +2931,34 @@
     </row>
     <row r="21" customHeight="1" spans="3:38">
       <c r="C21" s="1">
-        <v>10043</v>
+        <v>10033</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
       </c>
       <c r="E21" s="4">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I21" s="1">
+        <v>15</v>
+      </c>
+      <c r="J21" s="1">
+        <v>5</v>
+      </c>
+      <c r="K21" s="1">
+        <v>5</v>
+      </c>
+      <c r="L21" s="1">
         <v>10</v>
-      </c>
-      <c r="J21" s="1">
-        <v>5</v>
-      </c>
-      <c r="K21" s="1">
-        <v>5</v>
-      </c>
-      <c r="L21" s="1">
-        <v>20</v>
       </c>
       <c r="M21" s="1">
         <v>9999</v>
@@ -3008,25 +3017,25 @@
     </row>
     <row r="22" customHeight="1" spans="3:38">
       <c r="C22" s="1">
-        <v>10073</v>
+        <v>10043</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
       </c>
       <c r="E22" s="4">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I22" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J22" s="1">
         <v>5</v>
@@ -3035,7 +3044,7 @@
         <v>5</v>
       </c>
       <c r="L22" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M22" s="1">
         <v>9999</v>
@@ -3093,125 +3102,125 @@
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:38">
-      <c r="AC23" s="4"/>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:38">
-      <c r="AE24" s="1"/>
-      <c r="AF24" s="1"/>
-      <c r="AG24" s="1"/>
-      <c r="AH24" s="1"/>
-      <c r="AI24" s="1"/>
-      <c r="AJ24" s="1"/>
-      <c r="AK24" s="1"/>
-      <c r="AL24" s="1"/>
-    </row>
-    <row r="26" customHeight="1" spans="3:38">
-      <c r="C26" s="1">
-        <v>20011</v>
-      </c>
-      <c r="D26" s="1">
-        <v>2</v>
-      </c>
-      <c r="E26" s="4">
-        <v>2001</v>
-      </c>
-      <c r="F26" s="4" t="s">
+      <c r="C23" s="1">
+        <v>10073</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="4">
+        <v>1007</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="I26" s="1">
-        <v>100</v>
-      </c>
-      <c r="J26" s="1">
-        <v>1</v>
-      </c>
-      <c r="K26" s="1">
-        <v>5</v>
-      </c>
-      <c r="L26" s="1">
-        <v>0</v>
-      </c>
-      <c r="M26" s="1">
+      <c r="I23" s="1">
+        <v>5</v>
+      </c>
+      <c r="J23" s="1">
+        <v>5</v>
+      </c>
+      <c r="K23" s="1">
+        <v>5</v>
+      </c>
+      <c r="L23" s="1">
+        <v>30</v>
+      </c>
+      <c r="M23" s="1">
         <v>9999</v>
       </c>
-      <c r="N26" s="1">
-        <v>4</v>
-      </c>
-      <c r="O26" s="1">
-        <v>0</v>
-      </c>
-      <c r="P26" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="1">
-        <v>0</v>
-      </c>
-      <c r="R26" s="1">
-        <v>0</v>
-      </c>
-      <c r="S26" s="1">
-        <v>0</v>
-      </c>
-      <c r="T26" s="1">
-        <v>0</v>
-      </c>
-      <c r="U26" s="4">
-        <v>100</v>
-      </c>
-      <c r="V26" s="1">
-        <v>0</v>
-      </c>
-      <c r="W26" s="1">
-        <v>0</v>
-      </c>
-      <c r="X26" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD26" s="1">
-        <v>0</v>
-      </c>
+      <c r="N23" s="1">
+        <v>4</v>
+      </c>
+      <c r="O23" s="1">
+        <v>0</v>
+      </c>
+      <c r="P23" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>0</v>
+      </c>
+      <c r="R23" s="1">
+        <v>0</v>
+      </c>
+      <c r="S23" s="1">
+        <v>0</v>
+      </c>
+      <c r="T23" s="1">
+        <v>0</v>
+      </c>
+      <c r="U23" s="1">
+        <v>0</v>
+      </c>
+      <c r="V23" s="1">
+        <v>0</v>
+      </c>
+      <c r="W23" s="1">
+        <v>0</v>
+      </c>
+      <c r="X23" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="1">
+        <v>10</v>
+      </c>
+      <c r="AA23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:38">
+      <c r="AC24" s="4"/>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:38">
+      <c r="AE25" s="1"/>
+      <c r="AF25" s="1"/>
+      <c r="AG25" s="1"/>
+      <c r="AH25" s="1"/>
+      <c r="AI25" s="1"/>
+      <c r="AJ25" s="1"/>
+      <c r="AK25" s="1"/>
+      <c r="AL25" s="1"/>
     </row>
     <row r="27" customHeight="1" spans="3:38">
       <c r="C27" s="1">
-        <v>20021</v>
+        <v>20011</v>
       </c>
       <c r="D27" s="1">
         <v>2</v>
       </c>
       <c r="E27" s="4">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="I27" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J27" s="1">
         <v>1</v>
@@ -3247,7 +3256,7 @@
         <v>0</v>
       </c>
       <c r="U27" s="4">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="V27" s="1">
         <v>0</v>
@@ -3279,13 +3288,13 @@
     </row>
     <row r="28" customHeight="1" spans="3:38">
       <c r="C28" s="1">
-        <v>20031</v>
+        <v>20021</v>
       </c>
       <c r="D28" s="1">
         <v>2</v>
       </c>
       <c r="E28" s="4">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>81</v>
@@ -3297,7 +3306,7 @@
         <v>66</v>
       </c>
       <c r="I28" s="1">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J28" s="1">
         <v>1</v>
@@ -3306,7 +3315,7 @@
         <v>5</v>
       </c>
       <c r="L28" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M28" s="1">
         <v>9999</v>
@@ -3333,7 +3342,7 @@
         <v>0</v>
       </c>
       <c r="U28" s="4">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="V28" s="1">
         <v>0</v>
@@ -3365,13 +3374,13 @@
     </row>
     <row r="29" customHeight="1" spans="3:38">
       <c r="C29" s="1">
-        <v>20041</v>
+        <v>20031</v>
       </c>
       <c r="D29" s="1">
         <v>2</v>
       </c>
       <c r="E29" s="4">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>82</v>
@@ -3383,7 +3392,7 @@
         <v>66</v>
       </c>
       <c r="I29" s="1">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J29" s="1">
         <v>1</v>
@@ -3419,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="U29" s="4">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="V29" s="1">
         <v>0</v>
@@ -3451,13 +3460,13 @@
     </row>
     <row r="30" customHeight="1" spans="3:38">
       <c r="C30" s="1">
-        <v>20071</v>
+        <v>20041</v>
       </c>
       <c r="D30" s="1">
         <v>2</v>
       </c>
       <c r="E30" s="4">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>83</v>
@@ -3469,7 +3478,7 @@
         <v>66</v>
       </c>
       <c r="I30" s="1">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="J30" s="1">
         <v>1</v>
@@ -3478,7 +3487,7 @@
         <v>5</v>
       </c>
       <c r="L30" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M30" s="1">
         <v>9999</v>
@@ -3505,38 +3514,97 @@
         <v>0</v>
       </c>
       <c r="U30" s="4">
+        <v>2000</v>
+      </c>
+      <c r="V30" s="1">
+        <v>0</v>
+      </c>
+      <c r="W30" s="1">
+        <v>0</v>
+      </c>
+      <c r="X30" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:38">
+      <c r="C31" s="1">
+        <v>20071</v>
+      </c>
+      <c r="D31" s="1">
+        <v>2</v>
+      </c>
+      <c r="E31" s="4">
+        <v>2007</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I31" s="1">
+        <v>40</v>
+      </c>
+      <c r="J31" s="1">
+        <v>1</v>
+      </c>
+      <c r="K31" s="1">
+        <v>5</v>
+      </c>
+      <c r="L31" s="1">
+        <v>30</v>
+      </c>
+      <c r="M31" s="1">
+        <v>9999</v>
+      </c>
+      <c r="N31" s="1">
+        <v>4</v>
+      </c>
+      <c r="O31" s="1">
+        <v>0</v>
+      </c>
+      <c r="P31" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>0</v>
+      </c>
+      <c r="R31" s="1">
+        <v>0</v>
+      </c>
+      <c r="S31" s="1">
+        <v>0</v>
+      </c>
+      <c r="T31" s="1">
+        <v>0</v>
+      </c>
+      <c r="U31" s="4">
         <v>10000</v>
       </c>
-      <c r="V30" s="1">
-        <v>0</v>
-      </c>
-      <c r="W30" s="1">
-        <v>0</v>
-      </c>
-      <c r="X30" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA30" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB30" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC30" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD30" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:38">
-      <c r="F31" s="4"/>
+      <c r="V31" s="1">
+        <v>0</v>
+      </c>
       <c r="W31" s="1">
         <v>0</v>
       </c>
@@ -3546,69 +3614,24 @@
       <c r="Y31" s="1">
         <v>0</v>
       </c>
-      <c r="AC31" s="4"/>
+      <c r="Z31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="32" customHeight="1" spans="3:38">
-      <c r="C32" s="1">
-        <v>20022</v>
-      </c>
-      <c r="D32" s="1">
-        <v>2</v>
-      </c>
-      <c r="E32" s="4">
-        <v>2002</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I32" s="1">
-        <v>60</v>
-      </c>
-      <c r="J32" s="1">
-        <v>4</v>
-      </c>
-      <c r="K32" s="1">
-        <v>5</v>
-      </c>
-      <c r="L32" s="1">
-        <v>0</v>
-      </c>
-      <c r="M32" s="1">
-        <v>9999</v>
-      </c>
-      <c r="N32" s="1">
-        <v>4</v>
-      </c>
-      <c r="O32" s="1">
-        <v>0</v>
-      </c>
-      <c r="P32" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="1">
-        <v>0</v>
-      </c>
-      <c r="R32" s="1">
-        <v>0</v>
-      </c>
-      <c r="S32" s="1">
-        <v>0</v>
-      </c>
-      <c r="T32" s="1">
-        <v>0</v>
-      </c>
-      <c r="U32" s="1">
-        <v>0</v>
-      </c>
-      <c r="V32" s="4">
-        <v>10</v>
-      </c>
+      <c r="F32" s="4"/>
       <c r="W32" s="1">
         <v>0</v>
       </c>
@@ -3618,43 +3641,29 @@
       <c r="Y32" s="1">
         <v>0</v>
       </c>
-      <c r="Z32" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="1">
-        <v>0</v>
-      </c>
+      <c r="AC32" s="4"/>
     </row>
     <row r="33" customHeight="1" spans="3:38">
       <c r="C33" s="1">
-        <v>20032</v>
+        <v>20012</v>
       </c>
       <c r="D33" s="1">
         <v>2</v>
       </c>
       <c r="E33" s="4">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>70</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="I33" s="1">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J33" s="1">
         <v>4</v>
@@ -3663,7 +3672,7 @@
         <v>5</v>
       </c>
       <c r="L33" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M33" s="1">
         <v>9999</v>
@@ -3722,25 +3731,25 @@
     </row>
     <row r="34" customHeight="1" spans="3:38">
       <c r="C34" s="1">
-        <v>20042</v>
+        <v>20022</v>
       </c>
       <c r="D34" s="1">
         <v>2</v>
       </c>
       <c r="E34" s="4">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>70</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I34" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J34" s="1">
         <v>4</v>
@@ -3749,7 +3758,7 @@
         <v>5</v>
       </c>
       <c r="L34" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M34" s="1">
         <v>9999</v>
@@ -3779,7 +3788,7 @@
         <v>0</v>
       </c>
       <c r="V34" s="4">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="W34" s="1">
         <v>0</v>
@@ -3808,25 +3817,25 @@
     </row>
     <row r="35" customHeight="1" spans="3:38">
       <c r="C35" s="1">
-        <v>20052</v>
+        <v>20032</v>
       </c>
       <c r="D35" s="1">
         <v>2</v>
       </c>
       <c r="E35" s="4">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I35" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J35" s="1">
         <v>4</v>
@@ -3835,7 +3844,7 @@
         <v>5</v>
       </c>
       <c r="L35" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M35" s="1">
         <v>9999</v>
@@ -3861,10 +3870,10 @@
       <c r="T35" s="1">
         <v>0</v>
       </c>
-      <c r="U35" s="4">
-        <v>50</v>
-      </c>
-      <c r="V35" s="1">
+      <c r="U35" s="1">
+        <v>0</v>
+      </c>
+      <c r="V35" s="4">
         <v>5</v>
       </c>
       <c r="W35" s="1">
@@ -3894,25 +3903,25 @@
     </row>
     <row r="36" customHeight="1" spans="3:38">
       <c r="C36" s="1">
-        <v>20062</v>
+        <v>20042</v>
       </c>
       <c r="D36" s="1">
         <v>2</v>
       </c>
       <c r="E36" s="4">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>70</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I36" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J36" s="1">
         <v>4</v>
@@ -3921,7 +3930,7 @@
         <v>5</v>
       </c>
       <c r="L36" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M36" s="1">
         <v>9999</v>
@@ -3947,11 +3956,11 @@
       <c r="T36" s="1">
         <v>0</v>
       </c>
-      <c r="U36" s="4">
-        <v>0</v>
-      </c>
-      <c r="V36" s="1">
-        <v>1</v>
+      <c r="U36" s="1">
+        <v>0</v>
+      </c>
+      <c r="V36" s="4">
+        <v>20</v>
       </c>
       <c r="W36" s="1">
         <v>0</v>
@@ -3980,25 +3989,25 @@
     </row>
     <row r="37" customHeight="1" spans="3:38">
       <c r="C37" s="1">
-        <v>20072</v>
+        <v>20052</v>
       </c>
       <c r="D37" s="1">
         <v>2</v>
       </c>
       <c r="E37" s="4">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I37" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J37" s="1">
         <v>4</v>
@@ -4007,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="L37" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M37" s="1">
         <v>9999</v>
@@ -4033,11 +4042,11 @@
       <c r="T37" s="1">
         <v>0</v>
       </c>
-      <c r="U37" s="1">
-        <v>0</v>
-      </c>
-      <c r="V37" s="4">
-        <v>50</v>
+      <c r="U37" s="4">
+        <v>0</v>
+      </c>
+      <c r="V37" s="1">
+        <v>5</v>
       </c>
       <c r="W37" s="1">
         <v>0</v>
@@ -4065,8 +4074,66 @@
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:38">
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
+      <c r="C38" s="1">
+        <v>20062</v>
+      </c>
+      <c r="D38" s="1">
+        <v>2</v>
+      </c>
+      <c r="E38" s="4">
+        <v>2006</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I38" s="1">
+        <v>20</v>
+      </c>
+      <c r="J38" s="1">
+        <v>4</v>
+      </c>
+      <c r="K38" s="1">
+        <v>5</v>
+      </c>
+      <c r="L38" s="1">
+        <v>20</v>
+      </c>
+      <c r="M38" s="1">
+        <v>9999</v>
+      </c>
+      <c r="N38" s="1">
+        <v>4</v>
+      </c>
+      <c r="O38" s="1">
+        <v>0</v>
+      </c>
+      <c r="P38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>0</v>
+      </c>
+      <c r="R38" s="1">
+        <v>0</v>
+      </c>
+      <c r="S38" s="1">
+        <v>0</v>
+      </c>
+      <c r="T38" s="1">
+        <v>0</v>
+      </c>
+      <c r="U38" s="4">
+        <v>0</v>
+      </c>
+      <c r="V38" s="1">
+        <v>1</v>
+      </c>
       <c r="W38" s="1">
         <v>0</v>
       </c>
@@ -4074,39 +4141,54 @@
         <v>0</v>
       </c>
       <c r="Y38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:38">
       <c r="C39" s="1">
-        <v>20023</v>
+        <v>20072</v>
       </c>
       <c r="D39" s="1">
         <v>2</v>
       </c>
       <c r="E39" s="4">
-        <v>2002</v>
+        <v>2007</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I39" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J39" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K39" s="1">
         <v>5</v>
       </c>
       <c r="L39" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M39" s="1">
         <v>9999</v>
@@ -4135,8 +4217,8 @@
       <c r="U39" s="1">
         <v>0</v>
       </c>
-      <c r="V39" s="1">
-        <v>0</v>
+      <c r="V39" s="4">
+        <v>50</v>
       </c>
       <c r="W39" s="1">
         <v>0</v>
@@ -4148,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="Z39" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA39" s="1">
         <v>0</v>
@@ -4164,66 +4246,8 @@
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:38">
-      <c r="C40" s="1">
-        <v>20033</v>
-      </c>
-      <c r="D40" s="1">
-        <v>2</v>
-      </c>
-      <c r="E40" s="4">
-        <v>2003</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I40" s="1">
-        <v>15</v>
-      </c>
-      <c r="J40" s="1">
-        <v>5</v>
-      </c>
-      <c r="K40" s="1">
-        <v>5</v>
-      </c>
-      <c r="L40" s="1">
-        <v>10</v>
-      </c>
-      <c r="M40" s="1">
-        <v>9999</v>
-      </c>
-      <c r="N40" s="1">
-        <v>4</v>
-      </c>
-      <c r="O40" s="1">
-        <v>0</v>
-      </c>
-      <c r="P40" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="1">
-        <v>0</v>
-      </c>
-      <c r="R40" s="1">
-        <v>0</v>
-      </c>
-      <c r="S40" s="1">
-        <v>0</v>
-      </c>
-      <c r="T40" s="1">
-        <v>0</v>
-      </c>
-      <c r="U40" s="1">
-        <v>0</v>
-      </c>
-      <c r="V40" s="1">
-        <v>0</v>
-      </c>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
       <c r="W40" s="1">
         <v>0</v>
       </c>
@@ -4231,45 +4255,30 @@
         <v>0</v>
       </c>
       <c r="Y40" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z40" s="1">
-        <v>10</v>
-      </c>
-      <c r="AA40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD40" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:38">
       <c r="C41" s="1">
-        <v>20043</v>
+        <v>20023</v>
       </c>
       <c r="D41" s="1">
         <v>2</v>
       </c>
       <c r="E41" s="4">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I41" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J41" s="1">
         <v>5</v>
@@ -4278,7 +4287,7 @@
         <v>5</v>
       </c>
       <c r="L41" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M41" s="1">
         <v>9999</v>
@@ -4337,25 +4346,25 @@
     </row>
     <row r="42" customHeight="1" spans="3:38">
       <c r="C42" s="1">
-        <v>20073</v>
+        <v>20033</v>
       </c>
       <c r="D42" s="1">
         <v>2</v>
       </c>
       <c r="E42" s="4">
-        <v>2007</v>
+        <v>2003</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I42" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J42" s="1">
         <v>5</v>
@@ -4364,7 +4373,7 @@
         <v>5</v>
       </c>
       <c r="L42" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M42" s="1">
         <v>9999</v>
@@ -4421,209 +4430,209 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:38">
-      <c r="AE44" s="1"/>
-      <c r="AF44" s="1"/>
-      <c r="AG44" s="1"/>
-      <c r="AH44" s="1"/>
-      <c r="AI44" s="1"/>
-      <c r="AJ44" s="1"/>
-      <c r="AK44" s="1"/>
-      <c r="AL44" s="1"/>
-    </row>
-    <row r="46" customHeight="1" spans="3:38">
-      <c r="C46" s="1">
-        <v>30011</v>
-      </c>
-      <c r="D46" s="1">
-        <v>3</v>
-      </c>
-      <c r="E46" s="4">
-        <v>3001</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I46" s="1">
-        <v>100</v>
-      </c>
-      <c r="J46" s="1">
-        <v>1</v>
-      </c>
-      <c r="K46" s="1">
-        <v>5</v>
-      </c>
-      <c r="L46" s="1">
-        <v>0</v>
-      </c>
-      <c r="M46" s="1">
+    <row r="43" customHeight="1" spans="3:38">
+      <c r="C43" s="1">
+        <v>20043</v>
+      </c>
+      <c r="D43" s="1">
+        <v>2</v>
+      </c>
+      <c r="E43" s="4">
+        <v>2004</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I43" s="1">
+        <v>10</v>
+      </c>
+      <c r="J43" s="1">
+        <v>5</v>
+      </c>
+      <c r="K43" s="1">
+        <v>5</v>
+      </c>
+      <c r="L43" s="1">
+        <v>20</v>
+      </c>
+      <c r="M43" s="1">
         <v>9999</v>
       </c>
-      <c r="N46" s="1">
-        <v>4</v>
-      </c>
-      <c r="O46" s="1">
-        <v>0</v>
-      </c>
-      <c r="P46" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="1">
-        <v>0</v>
-      </c>
-      <c r="R46" s="1">
-        <v>0</v>
-      </c>
-      <c r="S46" s="1">
-        <v>0</v>
-      </c>
-      <c r="T46" s="1">
-        <v>0</v>
-      </c>
-      <c r="U46" s="4">
-        <v>100</v>
-      </c>
-      <c r="V46" s="1">
-        <v>0</v>
-      </c>
-      <c r="W46" s="1">
-        <v>0</v>
-      </c>
-      <c r="X46" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z46" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB46" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC46" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD46" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:38">
-      <c r="C47" s="1">
-        <v>30021</v>
-      </c>
-      <c r="D47" s="1">
-        <v>3</v>
-      </c>
-      <c r="E47" s="4">
-        <v>3002</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I47" s="1">
-        <v>90</v>
-      </c>
-      <c r="J47" s="1">
-        <v>1</v>
-      </c>
-      <c r="K47" s="1">
-        <v>5</v>
-      </c>
-      <c r="L47" s="1">
-        <v>0</v>
-      </c>
-      <c r="M47" s="1">
+      <c r="N43" s="1">
+        <v>4</v>
+      </c>
+      <c r="O43" s="1">
+        <v>0</v>
+      </c>
+      <c r="P43" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>0</v>
+      </c>
+      <c r="R43" s="1">
+        <v>0</v>
+      </c>
+      <c r="S43" s="1">
+        <v>0</v>
+      </c>
+      <c r="T43" s="1">
+        <v>0</v>
+      </c>
+      <c r="U43" s="1">
+        <v>0</v>
+      </c>
+      <c r="V43" s="1">
+        <v>0</v>
+      </c>
+      <c r="W43" s="1">
+        <v>0</v>
+      </c>
+      <c r="X43" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="1">
+        <v>10</v>
+      </c>
+      <c r="AA43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:38">
+      <c r="C44" s="1">
+        <v>20073</v>
+      </c>
+      <c r="D44" s="1">
+        <v>2</v>
+      </c>
+      <c r="E44" s="4">
+        <v>2007</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I44" s="1">
+        <v>5</v>
+      </c>
+      <c r="J44" s="1">
+        <v>5</v>
+      </c>
+      <c r="K44" s="1">
+        <v>5</v>
+      </c>
+      <c r="L44" s="1">
+        <v>30</v>
+      </c>
+      <c r="M44" s="1">
         <v>9999</v>
       </c>
-      <c r="N47" s="1">
-        <v>4</v>
-      </c>
-      <c r="O47" s="1">
-        <v>0</v>
-      </c>
-      <c r="P47" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="1">
-        <v>0</v>
-      </c>
-      <c r="R47" s="1">
-        <v>0</v>
-      </c>
-      <c r="S47" s="1">
-        <v>0</v>
-      </c>
-      <c r="T47" s="1">
-        <v>0</v>
-      </c>
-      <c r="U47" s="4">
-        <v>1000</v>
-      </c>
-      <c r="V47" s="1">
-        <v>0</v>
-      </c>
-      <c r="W47" s="1">
-        <v>0</v>
-      </c>
-      <c r="X47" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y47" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z47" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA47" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB47" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC47" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD47" s="1">
-        <v>0</v>
-      </c>
+      <c r="N44" s="1">
+        <v>4</v>
+      </c>
+      <c r="O44" s="1">
+        <v>0</v>
+      </c>
+      <c r="P44" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>0</v>
+      </c>
+      <c r="R44" s="1">
+        <v>0</v>
+      </c>
+      <c r="S44" s="1">
+        <v>0</v>
+      </c>
+      <c r="T44" s="1">
+        <v>0</v>
+      </c>
+      <c r="U44" s="1">
+        <v>0</v>
+      </c>
+      <c r="V44" s="1">
+        <v>0</v>
+      </c>
+      <c r="W44" s="1">
+        <v>0</v>
+      </c>
+      <c r="X44" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="1">
+        <v>10</v>
+      </c>
+      <c r="AA44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:38">
+      <c r="AE46" s="1"/>
+      <c r="AF46" s="1"/>
+      <c r="AG46" s="1"/>
+      <c r="AH46" s="1"/>
+      <c r="AI46" s="1"/>
+      <c r="AJ46" s="1"/>
+      <c r="AK46" s="1"/>
+      <c r="AL46" s="1"/>
     </row>
     <row r="48" customHeight="1" spans="3:38">
       <c r="C48" s="1">
-        <v>30031</v>
+        <v>30011</v>
       </c>
       <c r="D48" s="1">
         <v>3</v>
       </c>
       <c r="E48" s="4">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="I48" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J48" s="1">
         <v>1</v>
@@ -4632,7 +4641,7 @@
         <v>5</v>
       </c>
       <c r="L48" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M48" s="1">
         <v>9999</v>
@@ -4659,7 +4668,7 @@
         <v>0</v>
       </c>
       <c r="U48" s="4">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="V48" s="1">
         <v>0</v>
@@ -4691,13 +4700,13 @@
     </row>
     <row r="49" customHeight="1" spans="3:30">
       <c r="C49" s="1">
-        <v>30041</v>
+        <v>30021</v>
       </c>
       <c r="D49" s="1">
         <v>3</v>
       </c>
       <c r="E49" s="4">
-        <v>3004</v>
+        <v>3002</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>90</v>
@@ -4706,10 +4715,10 @@
         <v>63</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="I49" s="1">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="J49" s="1">
         <v>1</v>
@@ -4718,7 +4727,7 @@
         <v>5</v>
       </c>
       <c r="L49" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M49" s="1">
         <v>9999</v>
@@ -4745,7 +4754,7 @@
         <v>0</v>
       </c>
       <c r="U49" s="4">
-        <v>30000</v>
+        <v>1000</v>
       </c>
       <c r="V49" s="1">
         <v>0</v>
@@ -4777,25 +4786,25 @@
     </row>
     <row r="50" customHeight="1" spans="3:30">
       <c r="C50" s="1">
-        <v>30071</v>
+        <v>30031</v>
       </c>
       <c r="D50" s="1">
         <v>3</v>
       </c>
       <c r="E50" s="4">
-        <v>3007</v>
+        <v>3003</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I50" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="J50" s="1">
         <v>1</v>
@@ -4804,7 +4813,7 @@
         <v>5</v>
       </c>
       <c r="L50" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M50" s="1">
         <v>9999</v>
@@ -4831,7 +4840,7 @@
         <v>0</v>
       </c>
       <c r="U50" s="4">
-        <v>10000</v>
+        <v>800</v>
       </c>
       <c r="V50" s="1">
         <v>0</v>
@@ -4862,39 +4871,121 @@
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:30">
-      <c r="F51" s="4"/>
-      <c r="AC51" s="4"/>
+      <c r="C51" s="1">
+        <v>30041</v>
+      </c>
+      <c r="D51" s="1">
+        <v>3</v>
+      </c>
+      <c r="E51" s="4">
+        <v>3004</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I51" s="1">
+        <v>70</v>
+      </c>
+      <c r="J51" s="1">
+        <v>1</v>
+      </c>
+      <c r="K51" s="1">
+        <v>5</v>
+      </c>
+      <c r="L51" s="1">
+        <v>10</v>
+      </c>
+      <c r="M51" s="1">
+        <v>9999</v>
+      </c>
+      <c r="N51" s="1">
+        <v>4</v>
+      </c>
+      <c r="O51" s="1">
+        <v>0</v>
+      </c>
+      <c r="P51" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="1">
+        <v>0</v>
+      </c>
+      <c r="R51" s="1">
+        <v>0</v>
+      </c>
+      <c r="S51" s="1">
+        <v>0</v>
+      </c>
+      <c r="T51" s="1">
+        <v>0</v>
+      </c>
+      <c r="U51" s="4">
+        <v>30000</v>
+      </c>
+      <c r="V51" s="1">
+        <v>0</v>
+      </c>
+      <c r="W51" s="1">
+        <v>0</v>
+      </c>
+      <c r="X51" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="52" customHeight="1" spans="3:30">
       <c r="C52" s="1">
-        <v>30022</v>
+        <v>30071</v>
       </c>
       <c r="D52" s="1">
         <v>3</v>
       </c>
       <c r="E52" s="4">
-        <v>3002</v>
+        <v>3007</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="I52" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J52" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K52" s="1">
         <v>5</v>
       </c>
       <c r="L52" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M52" s="1">
         <v>9999</v>
@@ -4920,11 +5011,11 @@
       <c r="T52" s="1">
         <v>0</v>
       </c>
-      <c r="U52" s="1">
-        <v>0</v>
-      </c>
-      <c r="V52" s="4">
-        <v>10</v>
+      <c r="U52" s="4">
+        <v>10000</v>
+      </c>
+      <c r="V52" s="1">
+        <v>0</v>
       </c>
       <c r="W52" s="1">
         <v>0</v>
@@ -4952,112 +5043,30 @@
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:30">
-      <c r="C53" s="1">
-        <v>30032</v>
-      </c>
-      <c r="D53" s="1">
-        <v>3</v>
-      </c>
-      <c r="E53" s="4">
-        <v>3003</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I53" s="1">
-        <v>50</v>
-      </c>
-      <c r="J53" s="1">
-        <v>4</v>
-      </c>
-      <c r="K53" s="1">
-        <v>5</v>
-      </c>
-      <c r="L53" s="1">
-        <v>10</v>
-      </c>
-      <c r="M53" s="1">
-        <v>9999</v>
-      </c>
-      <c r="N53" s="1">
-        <v>4</v>
-      </c>
-      <c r="O53" s="1">
-        <v>0</v>
-      </c>
-      <c r="P53" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="1">
-        <v>0</v>
-      </c>
-      <c r="R53" s="1">
-        <v>0</v>
-      </c>
-      <c r="S53" s="1">
-        <v>0</v>
-      </c>
-      <c r="T53" s="1">
-        <v>0</v>
-      </c>
-      <c r="U53" s="1">
-        <v>0</v>
-      </c>
-      <c r="V53" s="4">
-        <v>10</v>
-      </c>
-      <c r="W53" s="1">
-        <v>0</v>
-      </c>
-      <c r="X53" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y53" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z53" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA53" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB53" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC53" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD53" s="1">
-        <v>0</v>
-      </c>
+      <c r="F53" s="4"/>
+      <c r="AC53" s="4"/>
     </row>
     <row r="54" customHeight="1" spans="3:30">
       <c r="C54" s="1">
-        <v>30042</v>
+        <v>30012</v>
       </c>
       <c r="D54" s="1">
         <v>3</v>
       </c>
       <c r="E54" s="4">
-        <v>3004</v>
+        <v>3001</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>70</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="I54" s="1">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="J54" s="1">
         <v>4</v>
@@ -5066,7 +5075,7 @@
         <v>5</v>
       </c>
       <c r="L54" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M54" s="1">
         <v>9999</v>
@@ -5096,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="V54" s="4">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="W54" s="1">
         <v>0</v>
@@ -5125,25 +5134,25 @@
     </row>
     <row r="55" customHeight="1" spans="3:30">
       <c r="C55" s="1">
-        <v>30052</v>
+        <v>30022</v>
       </c>
       <c r="D55" s="1">
         <v>3</v>
       </c>
       <c r="E55" s="4">
-        <v>3005</v>
+        <v>3002</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I55" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J55" s="1">
         <v>4</v>
@@ -5152,7 +5161,7 @@
         <v>5</v>
       </c>
       <c r="L55" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M55" s="1">
         <v>9999</v>
@@ -5178,11 +5187,11 @@
       <c r="T55" s="1">
         <v>0</v>
       </c>
-      <c r="U55" s="4">
-        <v>50</v>
-      </c>
-      <c r="V55" s="1">
-        <v>5</v>
+      <c r="U55" s="1">
+        <v>0</v>
+      </c>
+      <c r="V55" s="4">
+        <v>10</v>
       </c>
       <c r="W55" s="1">
         <v>0</v>
@@ -5211,25 +5220,25 @@
     </row>
     <row r="56" customHeight="1" spans="3:30">
       <c r="C56" s="1">
-        <v>30062</v>
+        <v>30032</v>
       </c>
       <c r="D56" s="1">
         <v>3</v>
       </c>
       <c r="E56" s="4">
-        <v>3006</v>
+        <v>3003</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>70</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I56" s="1">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J56" s="1">
         <v>4</v>
@@ -5238,7 +5247,7 @@
         <v>5</v>
       </c>
       <c r="L56" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M56" s="1">
         <v>9999</v>
@@ -5264,11 +5273,11 @@
       <c r="T56" s="1">
         <v>0</v>
       </c>
-      <c r="U56" s="4">
-        <v>0</v>
-      </c>
-      <c r="V56" s="1">
-        <v>1</v>
+      <c r="U56" s="1">
+        <v>0</v>
+      </c>
+      <c r="V56" s="4">
+        <v>5</v>
       </c>
       <c r="W56" s="1">
         <v>0</v>
@@ -5297,13 +5306,13 @@
     </row>
     <row r="57" customHeight="1" spans="3:30">
       <c r="C57" s="1">
-        <v>30072</v>
+        <v>30042</v>
       </c>
       <c r="D57" s="1">
         <v>3</v>
       </c>
       <c r="E57" s="4">
-        <v>3007</v>
+        <v>3004</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>92</v>
@@ -5312,19 +5321,19 @@
         <v>70</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I57" s="1">
+        <v>40</v>
+      </c>
+      <c r="J57" s="1">
+        <v>4</v>
+      </c>
+      <c r="K57" s="1">
+        <v>5</v>
+      </c>
+      <c r="L57" s="1">
         <v>10</v>
-      </c>
-      <c r="J57" s="1">
-        <v>4</v>
-      </c>
-      <c r="K57" s="1">
-        <v>5</v>
-      </c>
-      <c r="L57" s="1">
-        <v>30</v>
       </c>
       <c r="M57" s="1">
         <v>9999</v>
@@ -5354,67 +5363,149 @@
         <v>0</v>
       </c>
       <c r="V57" s="4">
+        <v>100</v>
+      </c>
+      <c r="W57" s="1">
+        <v>0</v>
+      </c>
+      <c r="X57" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:30">
+      <c r="C58" s="1">
+        <v>30052</v>
+      </c>
+      <c r="D58" s="1">
+        <v>3</v>
+      </c>
+      <c r="E58" s="4">
+        <v>3005</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I58" s="1">
+        <v>30</v>
+      </c>
+      <c r="J58" s="1">
+        <v>4</v>
+      </c>
+      <c r="K58" s="1">
+        <v>5</v>
+      </c>
+      <c r="L58" s="1">
+        <v>20</v>
+      </c>
+      <c r="M58" s="1">
+        <v>9999</v>
+      </c>
+      <c r="N58" s="1">
+        <v>4</v>
+      </c>
+      <c r="O58" s="1">
+        <v>0</v>
+      </c>
+      <c r="P58" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="1">
+        <v>0</v>
+      </c>
+      <c r="R58" s="1">
+        <v>0</v>
+      </c>
+      <c r="S58" s="1">
+        <v>0</v>
+      </c>
+      <c r="T58" s="1">
+        <v>0</v>
+      </c>
+      <c r="U58" s="4">
         <v>50</v>
       </c>
-      <c r="W57" s="1">
-        <v>0</v>
-      </c>
-      <c r="X57" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y57" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD57" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:30">
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
+      <c r="V58" s="1">
+        <v>5</v>
+      </c>
+      <c r="W58" s="1">
+        <v>0</v>
+      </c>
+      <c r="X58" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="59" customHeight="1" spans="3:30">
       <c r="C59" s="1">
-        <v>30023</v>
+        <v>30062</v>
       </c>
       <c r="D59" s="1">
         <v>3</v>
       </c>
       <c r="E59" s="4">
-        <v>3002</v>
+        <v>3006</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I59" s="1">
         <v>20</v>
       </c>
       <c r="J59" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K59" s="1">
         <v>5</v>
       </c>
       <c r="L59" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M59" s="1">
         <v>9999</v>
@@ -5440,11 +5531,11 @@
       <c r="T59" s="1">
         <v>0</v>
       </c>
-      <c r="U59" s="1">
+      <c r="U59" s="4">
         <v>0</v>
       </c>
       <c r="V59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W59" s="1">
         <v>0</v>
@@ -5456,7 +5547,7 @@
         <v>0</v>
       </c>
       <c r="Z59" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA59" s="1">
         <v>0</v>
@@ -5473,34 +5564,34 @@
     </row>
     <row r="60" customHeight="1" spans="3:30">
       <c r="C60" s="1">
-        <v>30033</v>
+        <v>30072</v>
       </c>
       <c r="D60" s="1">
         <v>3</v>
       </c>
       <c r="E60" s="4">
-        <v>3003</v>
+        <v>3007</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I60" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J60" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K60" s="1">
         <v>5</v>
       </c>
       <c r="L60" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M60" s="1">
         <v>9999</v>
@@ -5529,8 +5620,8 @@
       <c r="U60" s="1">
         <v>0</v>
       </c>
-      <c r="V60" s="1">
-        <v>0</v>
+      <c r="V60" s="4">
+        <v>20</v>
       </c>
       <c r="W60" s="1">
         <v>0</v>
@@ -5542,104 +5633,280 @@
         <v>0</v>
       </c>
       <c r="Z60" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB60" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:30">
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+    </row>
+    <row r="62" customHeight="1" spans="3:30">
+      <c r="C62" s="1">
+        <v>30023</v>
+      </c>
+      <c r="D62" s="1">
+        <v>3</v>
+      </c>
+      <c r="E62" s="4">
+        <v>3002</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I62" s="1">
+        <v>20</v>
+      </c>
+      <c r="J62" s="1">
+        <v>5</v>
+      </c>
+      <c r="K62" s="1">
+        <v>5</v>
+      </c>
+      <c r="L62" s="1">
+        <v>0</v>
+      </c>
+      <c r="M62" s="1">
+        <v>9999</v>
+      </c>
+      <c r="N62" s="1">
+        <v>4</v>
+      </c>
+      <c r="O62" s="1">
+        <v>0</v>
+      </c>
+      <c r="P62" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="1">
+        <v>0</v>
+      </c>
+      <c r="R62" s="1">
+        <v>0</v>
+      </c>
+      <c r="S62" s="1">
+        <v>0</v>
+      </c>
+      <c r="T62" s="1">
+        <v>0</v>
+      </c>
+      <c r="U62" s="1">
+        <v>0</v>
+      </c>
+      <c r="V62" s="1">
+        <v>0</v>
+      </c>
+      <c r="W62" s="1">
+        <v>0</v>
+      </c>
+      <c r="X62" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="1">
         <v>10</v>
       </c>
-      <c r="AA60" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB60" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC60" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD60" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:30">
-      <c r="C61" s="1">
+      <c r="AA62" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:30">
+      <c r="C63" s="1">
+        <v>30033</v>
+      </c>
+      <c r="D63" s="1">
+        <v>3</v>
+      </c>
+      <c r="E63" s="4">
+        <v>3003</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I63" s="1">
+        <v>15</v>
+      </c>
+      <c r="J63" s="1">
+        <v>5</v>
+      </c>
+      <c r="K63" s="1">
+        <v>5</v>
+      </c>
+      <c r="L63" s="1">
+        <v>10</v>
+      </c>
+      <c r="M63" s="1">
+        <v>9999</v>
+      </c>
+      <c r="N63" s="1">
+        <v>4</v>
+      </c>
+      <c r="O63" s="1">
+        <v>0</v>
+      </c>
+      <c r="P63" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="1">
+        <v>0</v>
+      </c>
+      <c r="R63" s="1">
+        <v>0</v>
+      </c>
+      <c r="S63" s="1">
+        <v>0</v>
+      </c>
+      <c r="T63" s="1">
+        <v>0</v>
+      </c>
+      <c r="U63" s="1">
+        <v>0</v>
+      </c>
+      <c r="V63" s="1">
+        <v>0</v>
+      </c>
+      <c r="W63" s="1">
+        <v>0</v>
+      </c>
+      <c r="X63" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="1">
+        <v>10</v>
+      </c>
+      <c r="AA63" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:30">
+      <c r="C64" s="1">
         <v>30073</v>
       </c>
-      <c r="D61" s="1">
+      <c r="D64" s="1">
         <v>3</v>
       </c>
-      <c r="E61" s="4">
+      <c r="E64" s="4">
         <v>3007</v>
       </c>
-      <c r="F61" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I61" s="1">
-        <v>5</v>
-      </c>
-      <c r="J61" s="1">
-        <v>5</v>
-      </c>
-      <c r="K61" s="1">
-        <v>5</v>
-      </c>
-      <c r="L61" s="1">
+      <c r="F64" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I64" s="1">
+        <v>5</v>
+      </c>
+      <c r="J64" s="1">
+        <v>5</v>
+      </c>
+      <c r="K64" s="1">
+        <v>5</v>
+      </c>
+      <c r="L64" s="1">
         <v>30</v>
       </c>
-      <c r="M61" s="1">
+      <c r="M64" s="1">
         <v>9999</v>
       </c>
-      <c r="N61" s="1">
-        <v>4</v>
-      </c>
-      <c r="O61" s="1">
-        <v>0</v>
-      </c>
-      <c r="P61" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="1">
-        <v>0</v>
-      </c>
-      <c r="R61" s="1">
-        <v>0</v>
-      </c>
-      <c r="S61" s="1">
-        <v>0</v>
-      </c>
-      <c r="T61" s="1">
-        <v>0</v>
-      </c>
-      <c r="U61" s="1">
-        <v>0</v>
-      </c>
-      <c r="V61" s="1">
-        <v>0</v>
-      </c>
-      <c r="W61" s="1">
-        <v>0</v>
-      </c>
-      <c r="X61" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y61" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="1">
+      <c r="N64" s="1">
+        <v>4</v>
+      </c>
+      <c r="O64" s="1">
+        <v>0</v>
+      </c>
+      <c r="P64" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="1">
+        <v>0</v>
+      </c>
+      <c r="R64" s="1">
+        <v>0</v>
+      </c>
+      <c r="S64" s="1">
+        <v>0</v>
+      </c>
+      <c r="T64" s="1">
+        <v>0</v>
+      </c>
+      <c r="U64" s="1">
+        <v>0</v>
+      </c>
+      <c r="V64" s="1">
+        <v>0</v>
+      </c>
+      <c r="W64" s="1">
+        <v>0</v>
+      </c>
+      <c r="X64" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="1">
         <v>10</v>
       </c>
-      <c r="AA61" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB61" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="1">
+      <c r="AA64" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD64" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -652,12 +652,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4926,7 +4926,7 @@
         <v>0</v>
       </c>
       <c r="U51" s="4">
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="V51" s="1">
         <v>0</v>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -5621,7 +5626,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="4">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="W60" s="1">
         <v>0</v>
